--- a/research/traditional_assets/database/data/jamaica/jamaica_recreation.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_recreation.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1385481776151525</v>
+        <v>0.1382355571711146</v>
       </c>
       <c r="C2">
-        <v>48.2166667020109</v>
+        <v>47.89346272083419</v>
       </c>
       <c r="D2">
-        <v>46.6866667020109</v>
+        <v>46.84456272083418</v>
       </c>
       <c r="E2">
-        <v>-1.31</v>
+        <v>-0.8289</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.4811</v>
       </c>
       <c r="G2">
         <v>1.53</v>
@@ -1451,28 +1451,28 @@
         <v>2.91</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02419933</v>
       </c>
       <c r="N2">
-        <v>2.91</v>
+        <v>2.88580067</v>
       </c>
       <c r="O2">
-        <v>0.7275</v>
+        <v>0.7214501675</v>
       </c>
       <c r="P2">
-        <v>2.1825</v>
+        <v>2.1643505025</v>
       </c>
       <c r="Q2">
-        <v>3.3425</v>
+        <v>3.3243505025</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1385481776151525</v>
+        <v>0.1392508153243582</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378592</v>
+        <v>0.9037408069995096</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>120.2512631548064</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1382355571711146</v>
+        <v>0.1379229367270767</v>
       </c>
       <c r="C3">
-        <v>47.89346272083419</v>
+        <v>47.57133038425046</v>
       </c>
       <c r="D3">
-        <v>46.84456272083418</v>
+        <v>47.00353038425046</v>
       </c>
       <c r="E3">
-        <v>-0.8289</v>
+        <v>-0.3478</v>
       </c>
       <c r="F3">
-        <v>0.4811</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="G3">
         <v>1.53</v>
@@ -1533,28 +1533,28 @@
         <v>2.91</v>
       </c>
       <c r="M3">
-        <v>0.02419933</v>
+        <v>0.04839866</v>
       </c>
       <c r="N3">
-        <v>2.88580067</v>
+        <v>2.86160134</v>
       </c>
       <c r="O3">
-        <v>0.7214501675</v>
+        <v>0.715400335</v>
       </c>
       <c r="P3">
-        <v>2.1643505025</v>
+        <v>2.146201005</v>
       </c>
       <c r="Q3">
-        <v>3.3243505025</v>
+        <v>3.306201005</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1392508153243582</v>
+        <v>0.1399677925786497</v>
       </c>
       <c r="T3">
-        <v>0.9037408069995096</v>
+        <v>0.9106745250216021</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>120.2512631548064</v>
+        <v>60.12563157740317</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1379229367270767</v>
+        <v>0.1376103162830389</v>
       </c>
       <c r="C4">
-        <v>47.57133038425046</v>
+        <v>47.25028063933041</v>
       </c>
       <c r="D4">
-        <v>47.00353038425046</v>
+        <v>47.16358063933041</v>
       </c>
       <c r="E4">
-        <v>-0.3478</v>
+        <v>0.1333</v>
       </c>
       <c r="F4">
-        <v>0.9622000000000001</v>
+        <v>1.4433</v>
       </c>
       <c r="G4">
         <v>1.53</v>
@@ -1615,28 +1615,28 @@
         <v>2.91</v>
       </c>
       <c r="M4">
-        <v>0.04839866</v>
+        <v>0.07259799</v>
       </c>
       <c r="N4">
-        <v>2.86160134</v>
+        <v>2.83740201</v>
       </c>
       <c r="O4">
-        <v>0.715400335</v>
+        <v>0.7093505025</v>
       </c>
       <c r="P4">
-        <v>2.146201005</v>
+        <v>2.1280515075</v>
       </c>
       <c r="Q4">
-        <v>3.306201005</v>
+        <v>3.2880515075</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1399677925786497</v>
+        <v>0.1406995528691122</v>
       </c>
       <c r="T4">
-        <v>0.9106745250216021</v>
+        <v>0.9177512063018817</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>60.12563157740317</v>
+        <v>40.08375438493545</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1376103162830389</v>
+        <v>0.137297695839001</v>
       </c>
       <c r="C5">
-        <v>47.25028063933041</v>
+        <v>46.93032458275634</v>
       </c>
       <c r="D5">
-        <v>47.16358063933041</v>
+        <v>47.32472458275634</v>
       </c>
       <c r="E5">
-        <v>0.1333</v>
+        <v>0.6144000000000001</v>
       </c>
       <c r="F5">
-        <v>1.4433</v>
+        <v>1.9244</v>
       </c>
       <c r="G5">
         <v>1.53</v>
@@ -1697,28 +1697,28 @@
         <v>2.91</v>
       </c>
       <c r="M5">
-        <v>0.07259799</v>
+        <v>0.09679732000000001</v>
       </c>
       <c r="N5">
-        <v>2.83740201</v>
+        <v>2.81320268</v>
       </c>
       <c r="O5">
-        <v>0.7093505025</v>
+        <v>0.7033006700000001</v>
       </c>
       <c r="P5">
-        <v>2.1280515075</v>
+        <v>2.10990201</v>
       </c>
       <c r="Q5">
-        <v>3.2880515075</v>
+        <v>3.26990201</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1406995528691122</v>
+        <v>0.141446558165626</v>
       </c>
       <c r="T5">
-        <v>0.9177512063018817</v>
+        <v>0.9249753184421674</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.08375438493545</v>
+        <v>30.06281578870159</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.137297695839001</v>
+        <v>0.1369850753949631</v>
       </c>
       <c r="C6">
-        <v>46.93032458275634</v>
+        <v>46.61147346338674</v>
       </c>
       <c r="D6">
-        <v>47.32472458275634</v>
+        <v>47.48697346338675</v>
       </c>
       <c r="E6">
-        <v>0.6144000000000001</v>
+        <v>1.0955</v>
       </c>
       <c r="F6">
-        <v>1.9244</v>
+        <v>2.4055</v>
       </c>
       <c r="G6">
         <v>1.53</v>
@@ -1779,28 +1779,28 @@
         <v>2.91</v>
       </c>
       <c r="M6">
-        <v>0.09679732000000001</v>
+        <v>0.12099665</v>
       </c>
       <c r="N6">
-        <v>2.81320268</v>
+        <v>2.78900335</v>
       </c>
       <c r="O6">
-        <v>0.7033006700000001</v>
+        <v>0.6972508375000001</v>
       </c>
       <c r="P6">
-        <v>2.10990201</v>
+        <v>2.0917525125</v>
       </c>
       <c r="Q6">
-        <v>3.26990201</v>
+        <v>3.2517525125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.141446558165626</v>
+        <v>0.1422092898894348</v>
       </c>
       <c r="T6">
-        <v>0.9249753184421674</v>
+        <v>0.9323515171538274</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.06281578870159</v>
+        <v>24.05025263096127</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1369850753949631</v>
+        <v>0.1366724549509252</v>
       </c>
       <c r="C7">
-        <v>46.61147346338674</v>
+        <v>46.2937386848739</v>
       </c>
       <c r="D7">
-        <v>47.48697346338675</v>
+        <v>47.6503386848739</v>
       </c>
       <c r="E7">
-        <v>1.0955</v>
+        <v>1.5766</v>
       </c>
       <c r="F7">
-        <v>2.4055</v>
+        <v>2.8866</v>
       </c>
       <c r="G7">
         <v>1.53</v>
@@ -1861,28 +1861,28 @@
         <v>2.91</v>
       </c>
       <c r="M7">
-        <v>0.12099665</v>
+        <v>0.14519598</v>
       </c>
       <c r="N7">
-        <v>2.78900335</v>
+        <v>2.76480402</v>
       </c>
       <c r="O7">
-        <v>0.6972508375000001</v>
+        <v>0.691201005</v>
       </c>
       <c r="P7">
-        <v>2.0917525125</v>
+        <v>2.073603015</v>
       </c>
       <c r="Q7">
-        <v>3.2517525125</v>
+        <v>3.233603015</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1422092898894348</v>
+        <v>0.1429882499477928</v>
       </c>
       <c r="T7">
-        <v>0.9323515171538274</v>
+        <v>0.9398846562636078</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.05025263096127</v>
+        <v>20.04187719246773</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1366724549509252</v>
+        <v>0.1363598345068873</v>
       </c>
       <c r="C8">
-        <v>46.2937386848739</v>
+        <v>45.97713180833571</v>
       </c>
       <c r="D8">
-        <v>47.6503386848739</v>
+        <v>47.8148318083357</v>
       </c>
       <c r="E8">
-        <v>1.5766</v>
+        <v>2.0577</v>
       </c>
       <c r="F8">
-        <v>2.8866</v>
+        <v>3.3677</v>
       </c>
       <c r="G8">
         <v>1.53</v>
@@ -1943,28 +1943,28 @@
         <v>2.91</v>
       </c>
       <c r="M8">
-        <v>0.14519598</v>
+        <v>0.16939531</v>
       </c>
       <c r="N8">
-        <v>2.76480402</v>
+        <v>2.74060469</v>
       </c>
       <c r="O8">
-        <v>0.691201005</v>
+        <v>0.6851511725</v>
       </c>
       <c r="P8">
-        <v>2.073603015</v>
+        <v>2.0554535175</v>
       </c>
       <c r="Q8">
-        <v>3.233603015</v>
+        <v>3.2154535175</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1429882499477928</v>
+        <v>0.1437839618353627</v>
       </c>
       <c r="T8">
-        <v>0.9398846562636078</v>
+        <v>0.9475797983649964</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.04187719246773</v>
+        <v>17.17875187925805</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1363598345068873</v>
+        <v>0.1360472140628495</v>
       </c>
       <c r="C9">
-        <v>45.97713180833571</v>
+        <v>45.66166455508296</v>
       </c>
       <c r="D9">
-        <v>47.8148318083357</v>
+        <v>47.98046455508295</v>
       </c>
       <c r="E9">
-        <v>2.0577</v>
+        <v>2.5388</v>
       </c>
       <c r="F9">
-        <v>3.3677</v>
+        <v>3.8488</v>
       </c>
       <c r="G9">
         <v>1.53</v>
@@ -2025,28 +2025,28 @@
         <v>2.91</v>
       </c>
       <c r="M9">
-        <v>0.16939531</v>
+        <v>0.19359464</v>
       </c>
       <c r="N9">
-        <v>2.74060469</v>
+        <v>2.71640536</v>
       </c>
       <c r="O9">
-        <v>0.6851511725</v>
+        <v>0.67910134</v>
       </c>
       <c r="P9">
-        <v>2.0554535175</v>
+        <v>2.03730402</v>
       </c>
       <c r="Q9">
-        <v>3.2154535175</v>
+        <v>3.19730402</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1437839618353627</v>
+        <v>0.1445969718074451</v>
       </c>
       <c r="T9">
-        <v>0.9475797983649964</v>
+        <v>0.9554422261642415</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.17875187925805</v>
+        <v>15.03140789435079</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1360472140628495</v>
+        <v>0.1357345936188116</v>
       </c>
       <c r="C10">
-        <v>45.66166455508296</v>
+        <v>45.34734880940373</v>
       </c>
       <c r="D10">
-        <v>47.98046455508295</v>
+        <v>48.14724880940373</v>
       </c>
       <c r="E10">
-        <v>2.5388</v>
+        <v>3.019899999999999</v>
       </c>
       <c r="F10">
-        <v>3.8488</v>
+        <v>4.329899999999999</v>
       </c>
       <c r="G10">
         <v>1.53</v>
@@ -2107,28 +2107,28 @@
         <v>2.91</v>
       </c>
       <c r="M10">
-        <v>0.19359464</v>
+        <v>0.2177939699999999</v>
       </c>
       <c r="N10">
-        <v>2.71640536</v>
+        <v>2.69220603</v>
       </c>
       <c r="O10">
-        <v>0.67910134</v>
+        <v>0.6730515075000001</v>
       </c>
       <c r="P10">
-        <v>2.03730402</v>
+        <v>2.0191545225</v>
       </c>
       <c r="Q10">
-        <v>3.19730402</v>
+        <v>3.1791545225</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1445969718074451</v>
+        <v>0.1454278501305622</v>
       </c>
       <c r="T10">
-        <v>0.9554422261642415</v>
+        <v>0.9634774545744587</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.03140789435079</v>
+        <v>13.36125146164516</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1357345936188116</v>
+        <v>0.1355344731747737</v>
       </c>
       <c r="C11">
-        <v>45.34734880940373</v>
+        <v>44.97362391809996</v>
       </c>
       <c r="D11">
-        <v>48.14724880940373</v>
+        <v>48.25462391809996</v>
       </c>
       <c r="E11">
-        <v>3.019899999999999</v>
+        <v>3.501</v>
       </c>
       <c r="F11">
-        <v>4.329899999999999</v>
+        <v>4.811</v>
       </c>
       <c r="G11">
         <v>1.53</v>
@@ -2189,45 +2189,45 @@
         <v>2.91</v>
       </c>
       <c r="M11">
-        <v>0.2177939699999999</v>
+        <v>0.2492098</v>
       </c>
       <c r="N11">
-        <v>2.69220603</v>
+        <v>2.6607902</v>
       </c>
       <c r="O11">
-        <v>0.6730515075000001</v>
+        <v>0.66519755</v>
       </c>
       <c r="P11">
-        <v>2.0191545225</v>
+        <v>1.99559265</v>
       </c>
       <c r="Q11">
-        <v>3.1791545225</v>
+        <v>3.15559265</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1454278501305622</v>
+        <v>0.1462771924164152</v>
       </c>
       <c r="T11">
-        <v>0.9634774545744587</v>
+        <v>0.9716912436160141</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.36125146164516</v>
+        <v>11.67690837198216</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1355344731747737</v>
+        <v>0.1352331027307358</v>
       </c>
       <c r="C12">
-        <v>44.97362391809996</v>
+        <v>44.65513168852322</v>
       </c>
       <c r="D12">
-        <v>48.25462391809996</v>
+        <v>48.41723168852322</v>
       </c>
       <c r="E12">
-        <v>3.501</v>
+        <v>3.9821</v>
       </c>
       <c r="F12">
-        <v>4.811</v>
+        <v>5.2921</v>
       </c>
       <c r="G12">
         <v>1.53</v>
@@ -2271,28 +2271,28 @@
         <v>2.91</v>
       </c>
       <c r="M12">
-        <v>0.2492098</v>
+        <v>0.27413078</v>
       </c>
       <c r="N12">
-        <v>2.6607902</v>
+        <v>2.63586922</v>
       </c>
       <c r="O12">
-        <v>0.66519755</v>
+        <v>0.658967305</v>
       </c>
       <c r="P12">
-        <v>1.99559265</v>
+        <v>1.976901915</v>
       </c>
       <c r="Q12">
-        <v>3.15559265</v>
+        <v>3.136901915</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1462771924164152</v>
+        <v>0.1471456210457706</v>
       </c>
       <c r="T12">
-        <v>0.9716912436160141</v>
+        <v>0.9800896121865934</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.67690837198216</v>
+        <v>10.61537124725651</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1352331027307358</v>
+        <v>0.1350847322866979</v>
       </c>
       <c r="C13">
-        <v>44.65513168852322</v>
+        <v>44.25448985847822</v>
       </c>
       <c r="D13">
-        <v>48.41723168852322</v>
+        <v>48.49768985847822</v>
       </c>
       <c r="E13">
-        <v>3.9821</v>
+        <v>4.463200000000001</v>
       </c>
       <c r="F13">
-        <v>5.2921</v>
+        <v>5.7732</v>
       </c>
       <c r="G13">
         <v>1.53</v>
@@ -2353,45 +2353,45 @@
         <v>2.91</v>
       </c>
       <c r="M13">
-        <v>0.27413078</v>
+        <v>0.3088662</v>
       </c>
       <c r="N13">
-        <v>2.63586922</v>
+        <v>2.6011338</v>
       </c>
       <c r="O13">
-        <v>0.658967305</v>
+        <v>0.6502834500000001</v>
       </c>
       <c r="P13">
-        <v>1.976901915</v>
+        <v>1.95085035</v>
       </c>
       <c r="Q13">
-        <v>3.136901915</v>
+        <v>3.110850350000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1471456210457706</v>
+        <v>0.1480337866894295</v>
       </c>
       <c r="T13">
-        <v>0.9800896121865934</v>
+        <v>0.9886788527701403</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.61537124725651</v>
+        <v>9.421555353094643</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1350847322866979</v>
+        <v>0.13479611184266</v>
       </c>
       <c r="C14">
-        <v>44.25448985847822</v>
+        <v>43.93067116540219</v>
       </c>
       <c r="D14">
-        <v>48.49768985847822</v>
+        <v>48.65497116540219</v>
       </c>
       <c r="E14">
-        <v>4.463200000000001</v>
+        <v>4.9443</v>
       </c>
       <c r="F14">
-        <v>5.7732</v>
+        <v>6.2543</v>
       </c>
       <c r="G14">
         <v>1.53</v>
@@ -2435,28 +2435,28 @@
         <v>2.91</v>
       </c>
       <c r="M14">
-        <v>0.3088662</v>
+        <v>0.33460505</v>
       </c>
       <c r="N14">
-        <v>2.6011338</v>
+        <v>2.57539495</v>
       </c>
       <c r="O14">
-        <v>0.6502834500000001</v>
+        <v>0.6438487375</v>
       </c>
       <c r="P14">
-        <v>1.95085035</v>
+        <v>1.9315462125</v>
       </c>
       <c r="Q14">
-        <v>3.110850350000001</v>
+        <v>3.0915462125</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1480337866894295</v>
+        <v>0.148942369934092</v>
       </c>
       <c r="T14">
-        <v>0.9886788527701403</v>
+        <v>0.9974655471602055</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.421555353094643</v>
+        <v>8.696820325933516</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.13479611184266</v>
+        <v>0.1345074913986222</v>
       </c>
       <c r="C15">
-        <v>43.93067116540219</v>
+        <v>43.60787593945228</v>
       </c>
       <c r="D15">
-        <v>48.65497116540219</v>
+        <v>48.81327593945228</v>
       </c>
       <c r="E15">
-        <v>4.9443</v>
+        <v>5.4254</v>
       </c>
       <c r="F15">
-        <v>6.2543</v>
+        <v>6.7354</v>
       </c>
       <c r="G15">
         <v>1.53</v>
@@ -2517,28 +2517,28 @@
         <v>2.91</v>
       </c>
       <c r="M15">
-        <v>0.33460505</v>
+        <v>0.3603439</v>
       </c>
       <c r="N15">
-        <v>2.57539495</v>
+        <v>2.5496561</v>
       </c>
       <c r="O15">
-        <v>0.6438487375</v>
+        <v>0.637414025</v>
       </c>
       <c r="P15">
-        <v>1.9315462125</v>
+        <v>1.912242075</v>
       </c>
       <c r="Q15">
-        <v>3.0915462125</v>
+        <v>3.072242075</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.148942369934092</v>
+        <v>0.1498720830216537</v>
       </c>
       <c r="T15">
-        <v>0.9974655471602055</v>
+        <v>1.006456583280272</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.696820325933516</v>
+        <v>8.075618874081121</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1345074913986222</v>
+        <v>0.1343088709545843</v>
       </c>
       <c r="C16">
-        <v>43.60787593945228</v>
+        <v>43.23631653620232</v>
       </c>
       <c r="D16">
-        <v>48.81327593945228</v>
+        <v>48.92281653620233</v>
       </c>
       <c r="E16">
-        <v>5.4254</v>
+        <v>5.906500000000001</v>
       </c>
       <c r="F16">
-        <v>6.7354</v>
+        <v>7.216500000000001</v>
       </c>
       <c r="G16">
         <v>1.53</v>
@@ -2599,45 +2599,45 @@
         <v>2.91</v>
       </c>
       <c r="M16">
-        <v>0.3603439</v>
+        <v>0.3918559500000001</v>
       </c>
       <c r="N16">
-        <v>2.5496561</v>
+        <v>2.51814405</v>
       </c>
       <c r="O16">
-        <v>0.637414025</v>
+        <v>0.6295360125</v>
       </c>
       <c r="P16">
-        <v>1.912242075</v>
+        <v>1.8886080375</v>
       </c>
       <c r="Q16">
-        <v>3.072242075</v>
+        <v>3.0486080375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1498720830216537</v>
+        <v>0.1508236717112756</v>
       </c>
       <c r="T16">
-        <v>1.006456583280272</v>
+        <v>1.015659173191399</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>8.075618874081121</v>
+        <v>7.426198326196143</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1343088709545843</v>
+        <v>0.1340262505105464</v>
       </c>
       <c r="C17">
-        <v>43.23631653620232</v>
+        <v>42.911933931003</v>
       </c>
       <c r="D17">
-        <v>48.92281653620233</v>
+        <v>49.079533931003</v>
       </c>
       <c r="E17">
-        <v>5.906499999999999</v>
+        <v>6.387600000000001</v>
       </c>
       <c r="F17">
-        <v>7.2165</v>
+        <v>7.6976</v>
       </c>
       <c r="G17">
         <v>1.53</v>
@@ -2681,28 +2681,28 @@
         <v>2.91</v>
       </c>
       <c r="M17">
-        <v>0.39185595</v>
+        <v>0.41797968</v>
       </c>
       <c r="N17">
-        <v>2.51814405</v>
+        <v>2.49202032</v>
       </c>
       <c r="O17">
-        <v>0.6295360125</v>
+        <v>0.62300508</v>
       </c>
       <c r="P17">
-        <v>1.8886080375</v>
+        <v>1.86901524</v>
       </c>
       <c r="Q17">
-        <v>3.0486080375</v>
+        <v>3.02901524</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1508236717112756</v>
+        <v>0.15179791727446</v>
       </c>
       <c r="T17">
-        <v>1.015659173191399</v>
+        <v>1.025080872386125</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.426198326196144</v>
+        <v>6.962060930808885</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1340262505105464</v>
+        <v>0.1337436300665085</v>
       </c>
       <c r="C18">
-        <v>42.911933931003</v>
+        <v>42.58855859693119</v>
       </c>
       <c r="D18">
-        <v>49.079533931003</v>
+        <v>49.23725859693119</v>
       </c>
       <c r="E18">
-        <v>6.387600000000001</v>
+        <v>6.8687</v>
       </c>
       <c r="F18">
-        <v>7.6976</v>
+        <v>8.178700000000001</v>
       </c>
       <c r="G18">
         <v>1.53</v>
@@ -2763,28 +2763,28 @@
         <v>2.91</v>
       </c>
       <c r="M18">
-        <v>0.41797968</v>
+        <v>0.4441034100000001</v>
       </c>
       <c r="N18">
-        <v>2.49202032</v>
+        <v>2.46589659</v>
       </c>
       <c r="O18">
-        <v>0.62300508</v>
+        <v>0.6164741475</v>
       </c>
       <c r="P18">
-        <v>1.86901524</v>
+        <v>1.8494224425</v>
       </c>
       <c r="Q18">
-        <v>3.02901524</v>
+        <v>3.0094224425</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.15179791727446</v>
+        <v>0.1527956386343476</v>
       </c>
       <c r="T18">
-        <v>1.025080872386125</v>
+        <v>1.034729600477109</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.962060930808885</v>
+        <v>6.55252793487895</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1337436300665085</v>
+        <v>0.1334610096224706</v>
       </c>
       <c r="C19">
-        <v>42.58855859693119</v>
+        <v>42.26620027635974</v>
       </c>
       <c r="D19">
-        <v>49.23725859693119</v>
+        <v>49.39600027635974</v>
       </c>
       <c r="E19">
-        <v>6.8687</v>
+        <v>7.3498</v>
       </c>
       <c r="F19">
-        <v>8.178700000000001</v>
+        <v>8.659800000000001</v>
       </c>
       <c r="G19">
         <v>1.53</v>
@@ -2845,28 +2845,28 @@
         <v>2.91</v>
       </c>
       <c r="M19">
-        <v>0.4441034100000001</v>
+        <v>0.47022714</v>
       </c>
       <c r="N19">
-        <v>2.46589659</v>
+        <v>2.43977286</v>
       </c>
       <c r="O19">
-        <v>0.6164741475</v>
+        <v>0.609943215</v>
       </c>
       <c r="P19">
-        <v>1.8494224425</v>
+        <v>1.829829645</v>
       </c>
       <c r="Q19">
-        <v>3.0094224425</v>
+        <v>2.989829645</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1527956386343476</v>
+        <v>0.1538176946615496</v>
       </c>
       <c r="T19">
-        <v>1.034729600477109</v>
+        <v>1.04461366339958</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.55252793487895</v>
+        <v>6.188498605163454</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1334610096224706</v>
+        <v>0.1333208891784328</v>
       </c>
       <c r="C20">
-        <v>42.26620027635974</v>
+        <v>41.86418299086812</v>
       </c>
       <c r="D20">
-        <v>49.39600027635974</v>
+        <v>49.47508299086812</v>
       </c>
       <c r="E20">
-        <v>7.349799999999998</v>
+        <v>7.8309</v>
       </c>
       <c r="F20">
-        <v>8.659799999999999</v>
+        <v>9.1409</v>
       </c>
       <c r="G20">
         <v>1.53</v>
@@ -2927,45 +2927,45 @@
         <v>2.91</v>
       </c>
       <c r="M20">
-        <v>0.4702271399999999</v>
+        <v>0.50549177</v>
       </c>
       <c r="N20">
-        <v>2.43977286</v>
+        <v>2.40450823</v>
       </c>
       <c r="O20">
-        <v>0.609943215</v>
+        <v>0.6011270575000001</v>
       </c>
       <c r="P20">
-        <v>1.829829645</v>
+        <v>1.8033811725</v>
       </c>
       <c r="Q20">
-        <v>2.989829645</v>
+        <v>2.9633811725</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1538176946615496</v>
+        <v>0.1548649866400405</v>
       </c>
       <c r="T20">
-        <v>1.04461366339958</v>
+        <v>1.054741777258409</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.188498605163455</v>
+        <v>5.756770283322318</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1333208891784328</v>
+        <v>0.1330457687343949</v>
       </c>
       <c r="C21">
-        <v>41.86418299086812</v>
+        <v>41.53909751167196</v>
       </c>
       <c r="D21">
-        <v>49.47508299086812</v>
+        <v>49.63109751167196</v>
       </c>
       <c r="E21">
-        <v>7.8309</v>
+        <v>8.311999999999999</v>
       </c>
       <c r="F21">
-        <v>9.1409</v>
+        <v>9.622</v>
       </c>
       <c r="G21">
         <v>1.53</v>
@@ -3009,28 +3009,28 @@
         <v>2.91</v>
       </c>
       <c r="M21">
-        <v>0.50549177</v>
+        <v>0.5320966</v>
       </c>
       <c r="N21">
-        <v>2.40450823</v>
+        <v>2.3779034</v>
       </c>
       <c r="O21">
-        <v>0.6011270575000001</v>
+        <v>0.59447585</v>
       </c>
       <c r="P21">
-        <v>1.8033811725</v>
+        <v>1.78342755</v>
       </c>
       <c r="Q21">
-        <v>2.9633811725</v>
+        <v>2.94342755</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1548649866400405</v>
+        <v>0.1559384609179936</v>
       </c>
       <c r="T21">
-        <v>1.054741777258409</v>
+        <v>1.065123093963708</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.756770283322318</v>
+        <v>5.468931769156202</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1330457687343949</v>
+        <v>0.132770648290357</v>
       </c>
       <c r="C22">
-        <v>41.53909751167196</v>
+        <v>41.21499909615956</v>
       </c>
       <c r="D22">
-        <v>49.63109751167196</v>
+        <v>49.78809909615956</v>
       </c>
       <c r="E22">
-        <v>8.311999999999999</v>
+        <v>8.793100000000001</v>
       </c>
       <c r="F22">
-        <v>9.622</v>
+        <v>10.1031</v>
       </c>
       <c r="G22">
         <v>1.53</v>
@@ -3091,28 +3091,28 @@
         <v>2.91</v>
       </c>
       <c r="M22">
-        <v>0.5320966</v>
+        <v>0.5587014300000001</v>
       </c>
       <c r="N22">
-        <v>2.3779034</v>
+        <v>2.35129857</v>
       </c>
       <c r="O22">
-        <v>0.59447585</v>
+        <v>0.5878246425</v>
       </c>
       <c r="P22">
-        <v>1.78342755</v>
+        <v>1.7634739275</v>
       </c>
       <c r="Q22">
-        <v>2.94342755</v>
+        <v>2.9234739275</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1559384609179936</v>
+        <v>0.1570391117599456</v>
       </c>
       <c r="T22">
-        <v>1.065123093963708</v>
+        <v>1.075767228813445</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.468931769156202</v>
+        <v>5.20850644681543</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.132770648290357</v>
+        <v>0.1324955278463191</v>
       </c>
       <c r="C23">
-        <v>41.21499909615956</v>
+        <v>40.8918971414038</v>
       </c>
       <c r="D23">
-        <v>49.78809909615956</v>
+        <v>49.9460971414038</v>
       </c>
       <c r="E23">
-        <v>8.793099999999999</v>
+        <v>9.274199999999999</v>
       </c>
       <c r="F23">
-        <v>10.1031</v>
+        <v>10.5842</v>
       </c>
       <c r="G23">
         <v>1.53</v>
@@ -3173,28 +3173,28 @@
         <v>2.91</v>
       </c>
       <c r="M23">
-        <v>0.5587014299999999</v>
+        <v>0.58530626</v>
       </c>
       <c r="N23">
-        <v>2.35129857</v>
+        <v>2.32469374</v>
       </c>
       <c r="O23">
-        <v>0.5878246425</v>
+        <v>0.5811734350000001</v>
       </c>
       <c r="P23">
-        <v>1.7634739275</v>
+        <v>1.743520305</v>
       </c>
       <c r="Q23">
-        <v>2.9234739275</v>
+        <v>2.903520305</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1570391117599456</v>
+        <v>0.1581679844183578</v>
       </c>
       <c r="T23">
-        <v>1.075767228813445</v>
+        <v>1.086684290197791</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.208506446815431</v>
+        <v>4.971756153778366</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1324955278463191</v>
+        <v>0.1322204074022812</v>
       </c>
       <c r="C24">
-        <v>40.8918971414038</v>
+        <v>40.56980116414044</v>
       </c>
       <c r="D24">
-        <v>49.9460971414038</v>
+        <v>50.10510116414044</v>
       </c>
       <c r="E24">
-        <v>9.274199999999999</v>
+        <v>9.7553</v>
       </c>
       <c r="F24">
-        <v>10.5842</v>
+        <v>11.0653</v>
       </c>
       <c r="G24">
         <v>1.53</v>
@@ -3255,28 +3255,28 @@
         <v>2.91</v>
       </c>
       <c r="M24">
-        <v>0.58530626</v>
+        <v>0.6119110900000001</v>
       </c>
       <c r="N24">
-        <v>2.32469374</v>
+        <v>2.29808891</v>
       </c>
       <c r="O24">
-        <v>0.5811734350000001</v>
+        <v>0.5745222275</v>
       </c>
       <c r="P24">
-        <v>1.743520305</v>
+        <v>1.7235666825</v>
       </c>
       <c r="Q24">
-        <v>2.903520305</v>
+        <v>2.8835666825</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1581679844183578</v>
+        <v>0.1593261784445211</v>
       </c>
       <c r="T24">
-        <v>1.086684290197791</v>
+        <v>1.097884911618094</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.971756153778366</v>
+        <v>4.755592842744523</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1322204074022812</v>
+        <v>0.1319452869582434</v>
       </c>
       <c r="C25">
-        <v>40.56980116414044</v>
+        <v>40.2487208026788</v>
       </c>
       <c r="D25">
-        <v>50.10510116414044</v>
+        <v>50.26512080267879</v>
       </c>
       <c r="E25">
-        <v>9.7553</v>
+        <v>10.2364</v>
       </c>
       <c r="F25">
-        <v>11.0653</v>
+        <v>11.5464</v>
       </c>
       <c r="G25">
         <v>1.53</v>
@@ -3337,28 +3337,28 @@
         <v>2.91</v>
       </c>
       <c r="M25">
-        <v>0.6119110900000001</v>
+        <v>0.63851592</v>
       </c>
       <c r="N25">
-        <v>2.29808891</v>
+        <v>2.27148408</v>
       </c>
       <c r="O25">
-        <v>0.5745222275</v>
+        <v>0.56787102</v>
       </c>
       <c r="P25">
-        <v>1.7235666825</v>
+        <v>1.70361306</v>
       </c>
       <c r="Q25">
-        <v>2.8835666825</v>
+        <v>2.86361306</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1593261784445211</v>
+        <v>0.1605148512608465</v>
       </c>
       <c r="T25">
-        <v>1.097884911618094</v>
+        <v>1.109380286233668</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.755592842744523</v>
+        <v>4.557443140963501</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1319452869582434</v>
+        <v>0.1321389165142055</v>
       </c>
       <c r="C26">
-        <v>40.2487208026788</v>
+        <v>39.65489280684156</v>
       </c>
       <c r="D26">
-        <v>50.26512080267879</v>
+        <v>50.15239280684156</v>
       </c>
       <c r="E26">
-        <v>10.2364</v>
+        <v>10.7175</v>
       </c>
       <c r="F26">
-        <v>11.5464</v>
+        <v>12.0275</v>
       </c>
       <c r="G26">
         <v>1.53</v>
@@ -3419,45 +3419,45 @@
         <v>2.91</v>
       </c>
       <c r="M26">
-        <v>0.63851592</v>
+        <v>0.6951895</v>
       </c>
       <c r="N26">
-        <v>2.27148408</v>
+        <v>2.2148105</v>
       </c>
       <c r="O26">
-        <v>0.56787102</v>
+        <v>0.553702625</v>
       </c>
       <c r="P26">
-        <v>1.70361306</v>
+        <v>1.661107875</v>
       </c>
       <c r="Q26">
-        <v>2.86361306</v>
+        <v>2.821107875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1605148512608465</v>
+        <v>0.1617352220189406</v>
       </c>
       <c r="T26">
-        <v>1.109380286233668</v>
+        <v>1.121182204172324</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.557443140963501</v>
+        <v>4.185909021928554</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1321389165142055</v>
+        <v>0.1318825460701676</v>
       </c>
       <c r="C27">
-        <v>39.65489280684156</v>
+        <v>39.32315631664032</v>
       </c>
       <c r="D27">
-        <v>50.15239280684156</v>
+        <v>50.30175631664032</v>
       </c>
       <c r="E27">
-        <v>10.7175</v>
+        <v>11.1986</v>
       </c>
       <c r="F27">
-        <v>12.0275</v>
+        <v>12.5086</v>
       </c>
       <c r="G27">
         <v>1.53</v>
@@ -3501,28 +3501,28 @@
         <v>2.91</v>
       </c>
       <c r="M27">
-        <v>0.6951895</v>
+        <v>0.7229970800000001</v>
       </c>
       <c r="N27">
-        <v>2.2148105</v>
+        <v>2.18700292</v>
       </c>
       <c r="O27">
-        <v>0.553702625</v>
+        <v>0.5467507300000001</v>
       </c>
       <c r="P27">
-        <v>1.661107875</v>
+        <v>1.64025219</v>
       </c>
       <c r="Q27">
-        <v>2.821107875</v>
+        <v>2.80025219</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1617352220189406</v>
+        <v>0.1629885757704967</v>
       </c>
       <c r="T27">
-        <v>1.121182204172324</v>
+        <v>1.133303092866079</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.185909021928554</v>
+        <v>4.024912521085147</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1318825460701676</v>
+        <v>0.1323349256261297</v>
       </c>
       <c r="C28">
-        <v>39.32315631664032</v>
+        <v>38.57909328729709</v>
       </c>
       <c r="D28">
-        <v>50.30175631664032</v>
+        <v>50.03879328729709</v>
       </c>
       <c r="E28">
-        <v>11.1986</v>
+        <v>11.6797</v>
       </c>
       <c r="F28">
-        <v>12.5086</v>
+        <v>12.9897</v>
       </c>
       <c r="G28">
         <v>1.53</v>
@@ -3583,45 +3583,45 @@
         <v>2.91</v>
       </c>
       <c r="M28">
-        <v>0.7229970800000001</v>
+        <v>0.79626861</v>
       </c>
       <c r="N28">
-        <v>2.18700292</v>
+        <v>2.11373139</v>
       </c>
       <c r="O28">
-        <v>0.5467507300000001</v>
+        <v>0.5284328475</v>
       </c>
       <c r="P28">
-        <v>1.64025219</v>
+        <v>1.5852985425</v>
       </c>
       <c r="Q28">
-        <v>2.80025219</v>
+        <v>2.7452985425</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1629885757704967</v>
+        <v>0.1642762679809996</v>
       </c>
       <c r="T28">
-        <v>1.133303092866079</v>
+        <v>1.145756060702128</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.024912521085147</v>
+        <v>3.6545456689546</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1323349256261297</v>
+        <v>0.1321048051820918</v>
       </c>
       <c r="C29">
-        <v>38.57909328729709</v>
+        <v>38.23141516694908</v>
       </c>
       <c r="D29">
-        <v>50.03879328729709</v>
+        <v>50.17221516694908</v>
       </c>
       <c r="E29">
-        <v>11.6797</v>
+        <v>12.1608</v>
       </c>
       <c r="F29">
-        <v>12.9897</v>
+        <v>13.4708</v>
       </c>
       <c r="G29">
         <v>1.53</v>
@@ -3665,28 +3665,28 @@
         <v>2.91</v>
       </c>
       <c r="M29">
-        <v>0.79626861</v>
+        <v>0.82576004</v>
       </c>
       <c r="N29">
-        <v>2.11373139</v>
+        <v>2.08423996</v>
       </c>
       <c r="O29">
-        <v>0.5284328475</v>
+        <v>0.52105999</v>
       </c>
       <c r="P29">
-        <v>1.5852985425</v>
+        <v>1.56317997</v>
       </c>
       <c r="Q29">
-        <v>2.7452985425</v>
+        <v>2.72317997</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1642762679809996</v>
+        <v>0.165599729419572</v>
       </c>
       <c r="T29">
-        <v>1.145756060702128</v>
+        <v>1.158554944311402</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.6545456689546</v>
+        <v>3.524026180777651</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1321048051820918</v>
+        <v>0.1324836847380539</v>
       </c>
       <c r="C30">
-        <v>38.23141516694908</v>
+        <v>37.53102099802292</v>
       </c>
       <c r="D30">
-        <v>50.17221516694908</v>
+        <v>49.95292099802292</v>
       </c>
       <c r="E30">
-        <v>12.1608</v>
+        <v>12.6419</v>
       </c>
       <c r="F30">
-        <v>13.4708</v>
+        <v>13.9519</v>
       </c>
       <c r="G30">
         <v>1.53</v>
@@ -3747,45 +3747,45 @@
         <v>2.91</v>
       </c>
       <c r="M30">
-        <v>0.82576004</v>
+        <v>0.8943167900000002</v>
       </c>
       <c r="N30">
-        <v>2.08423996</v>
+        <v>2.01568321</v>
       </c>
       <c r="O30">
-        <v>0.52105999</v>
+        <v>0.5039208024999999</v>
       </c>
       <c r="P30">
-        <v>1.56317997</v>
+        <v>1.5117624075</v>
       </c>
       <c r="Q30">
-        <v>2.72317997</v>
+        <v>2.6717624075</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.165599729419572</v>
+        <v>0.1669604714620478</v>
       </c>
       <c r="T30">
-        <v>1.158554944311402</v>
+        <v>1.17171435985333</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.524026180777651</v>
+        <v>3.253880540473806</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1324836847380539</v>
+        <v>0.132274564294016</v>
       </c>
       <c r="C31">
-        <v>37.53102099802292</v>
+        <v>37.17072157221926</v>
       </c>
       <c r="D31">
-        <v>49.95292099802292</v>
+        <v>50.07372157221926</v>
       </c>
       <c r="E31">
-        <v>12.6419</v>
+        <v>13.123</v>
       </c>
       <c r="F31">
-        <v>13.9519</v>
+        <v>14.433</v>
       </c>
       <c r="G31">
         <v>1.53</v>
@@ -3829,28 +3829,28 @@
         <v>2.91</v>
       </c>
       <c r="M31">
-        <v>0.89431679</v>
+        <v>0.9251553</v>
       </c>
       <c r="N31">
-        <v>2.01568321</v>
+        <v>1.9848447</v>
       </c>
       <c r="O31">
-        <v>0.5039208025</v>
+        <v>0.496211175</v>
       </c>
       <c r="P31">
-        <v>1.5117624075</v>
+        <v>1.488633525</v>
       </c>
       <c r="Q31">
-        <v>2.6717624075</v>
+        <v>2.648633525</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1669604714620478</v>
+        <v>0.1683600918485944</v>
       </c>
       <c r="T31">
-        <v>1.17171435985333</v>
+        <v>1.185249758696457</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.253880540473807</v>
+        <v>3.145417855791347</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.132274564294016</v>
+        <v>0.1320654438499782</v>
       </c>
       <c r="C32">
-        <v>37.17072157221926</v>
+        <v>36.81100782403085</v>
       </c>
       <c r="D32">
-        <v>50.07372157221926</v>
+        <v>50.19510782403084</v>
       </c>
       <c r="E32">
-        <v>13.123</v>
+        <v>13.6041</v>
       </c>
       <c r="F32">
-        <v>14.433</v>
+        <v>14.9141</v>
       </c>
       <c r="G32">
         <v>1.53</v>
@@ -3911,28 +3911,28 @@
         <v>2.91</v>
       </c>
       <c r="M32">
-        <v>0.9251553</v>
+        <v>0.9559938100000001</v>
       </c>
       <c r="N32">
-        <v>1.9848447</v>
+        <v>1.95400619</v>
       </c>
       <c r="O32">
-        <v>0.496211175</v>
+        <v>0.4885015475</v>
       </c>
       <c r="P32">
-        <v>1.488633525</v>
+        <v>1.4655046425</v>
       </c>
       <c r="Q32">
-        <v>2.648633525</v>
+        <v>2.6255046425</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1683600918485944</v>
+        <v>0.1698002809419974</v>
       </c>
       <c r="T32">
-        <v>1.185249758696457</v>
+        <v>1.199177487940833</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.145417855791347</v>
+        <v>3.043952763669045</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1320654438499782</v>
+        <v>0.1337283234059403</v>
       </c>
       <c r="C33">
-        <v>36.81100782403085</v>
+        <v>35.38062987380147</v>
       </c>
       <c r="D33">
-        <v>50.19510782403084</v>
+        <v>49.24582987380148</v>
       </c>
       <c r="E33">
-        <v>13.6041</v>
+        <v>14.0852</v>
       </c>
       <c r="F33">
-        <v>14.9141</v>
+        <v>15.3952</v>
       </c>
       <c r="G33">
         <v>1.53</v>
@@ -3993,45 +3993,45 @@
         <v>2.91</v>
       </c>
       <c r="M33">
-        <v>0.9559938100000001</v>
+        <v>1.10691488</v>
       </c>
       <c r="N33">
-        <v>1.95400619</v>
+        <v>1.80308512</v>
       </c>
       <c r="O33">
-        <v>0.4885015475</v>
+        <v>0.45077128</v>
       </c>
       <c r="P33">
-        <v>1.4655046425</v>
+        <v>1.35231384</v>
       </c>
       <c r="Q33">
-        <v>2.6255046425</v>
+        <v>2.51231384</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1698002809419974</v>
+        <v>0.1712828285381475</v>
       </c>
       <c r="T33">
-        <v>1.199177487940833</v>
+        <v>1.213514856280633</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.043952763669045</v>
+        <v>2.628928432148278</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1337283234059403</v>
+        <v>0.1335777029619024</v>
       </c>
       <c r="C34">
-        <v>35.38062987380147</v>
+        <v>34.98403229881738</v>
       </c>
       <c r="D34">
-        <v>49.24582987380148</v>
+        <v>49.33033229881737</v>
       </c>
       <c r="E34">
-        <v>14.0852</v>
+        <v>14.5663</v>
       </c>
       <c r="F34">
-        <v>15.3952</v>
+        <v>15.8763</v>
       </c>
       <c r="G34">
         <v>1.53</v>
@@ -4075,28 +4075,28 @@
         <v>2.91</v>
       </c>
       <c r="M34">
-        <v>1.10691488</v>
+        <v>1.14150597</v>
       </c>
       <c r="N34">
-        <v>1.80308512</v>
+        <v>1.76849403</v>
       </c>
       <c r="O34">
-        <v>0.45077128</v>
+        <v>0.4421235075</v>
       </c>
       <c r="P34">
-        <v>1.35231384</v>
+        <v>1.3263705225</v>
       </c>
       <c r="Q34">
-        <v>2.51231384</v>
+        <v>2.4863705225</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1712828285381475</v>
+        <v>0.1728096312864216</v>
       </c>
       <c r="T34">
-        <v>1.213514856280633</v>
+        <v>1.228280205764904</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.628928432148278</v>
+        <v>2.549263934204391</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1335777029619024</v>
+        <v>0.1344215825178645</v>
       </c>
       <c r="C35">
-        <v>34.98403229881738</v>
+        <v>34.0331950437035</v>
       </c>
       <c r="D35">
-        <v>49.33033229881737</v>
+        <v>48.8605950437035</v>
       </c>
       <c r="E35">
-        <v>14.5663</v>
+        <v>15.0474</v>
       </c>
       <c r="F35">
-        <v>15.8763</v>
+        <v>16.3574</v>
       </c>
       <c r="G35">
         <v>1.53</v>
@@ -4157,45 +4157,45 @@
         <v>2.91</v>
       </c>
       <c r="M35">
-        <v>1.14150597</v>
+        <v>1.23989092</v>
       </c>
       <c r="N35">
-        <v>1.76849403</v>
+        <v>1.67010908</v>
       </c>
       <c r="O35">
-        <v>0.4421235075</v>
+        <v>0.41752727</v>
       </c>
       <c r="P35">
-        <v>1.3263705225</v>
+        <v>1.25258181</v>
       </c>
       <c r="Q35">
-        <v>2.4863705225</v>
+        <v>2.41258181</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1728096312864216</v>
+        <v>0.1743827007846433</v>
       </c>
       <c r="T35">
-        <v>1.228280205764904</v>
+        <v>1.243492990082032</v>
       </c>
       <c r="U35">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.549263934204391</v>
+        <v>2.346980652136721</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1344215825178645</v>
+        <v>0.1343002120738267</v>
       </c>
       <c r="C36">
-        <v>34.0331950437035</v>
+        <v>33.6191031556328</v>
       </c>
       <c r="D36">
-        <v>48.8605950437035</v>
+        <v>48.9276031556328</v>
       </c>
       <c r="E36">
-        <v>15.0474</v>
+        <v>15.5285</v>
       </c>
       <c r="F36">
-        <v>16.3574</v>
+        <v>16.8385</v>
       </c>
       <c r="G36">
         <v>1.53</v>
@@ -4239,28 +4239,28 @@
         <v>2.91</v>
       </c>
       <c r="M36">
-        <v>1.23989092</v>
+        <v>1.2763583</v>
       </c>
       <c r="N36">
-        <v>1.67010908</v>
+        <v>1.6336417</v>
       </c>
       <c r="O36">
-        <v>0.41752727</v>
+        <v>0.408410425</v>
       </c>
       <c r="P36">
-        <v>1.25258181</v>
+        <v>1.225231275</v>
       </c>
       <c r="Q36">
-        <v>2.41258181</v>
+        <v>2.385231275</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1743827007846433</v>
+        <v>0.1760041724212718</v>
       </c>
       <c r="T36">
-        <v>1.243492990082032</v>
+        <v>1.259173860070456</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.346980652136721</v>
+        <v>2.279924062075673</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1343002120738267</v>
+        <v>0.1341788416297888</v>
       </c>
       <c r="C37">
-        <v>33.6191031556328</v>
+        <v>33.20519531170997</v>
       </c>
       <c r="D37">
-        <v>48.9276031556328</v>
+        <v>48.99479531170997</v>
       </c>
       <c r="E37">
-        <v>15.5285</v>
+        <v>16.0096</v>
       </c>
       <c r="F37">
-        <v>16.8385</v>
+        <v>17.3196</v>
       </c>
       <c r="G37">
         <v>1.53</v>
@@ -4321,28 +4321,28 @@
         <v>2.91</v>
       </c>
       <c r="M37">
-        <v>1.2763583</v>
+        <v>1.31282568</v>
       </c>
       <c r="N37">
-        <v>1.6336417</v>
+        <v>1.59717432</v>
       </c>
       <c r="O37">
-        <v>0.408410425</v>
+        <v>0.39929358</v>
       </c>
       <c r="P37">
-        <v>1.225231275</v>
+        <v>1.19788074</v>
       </c>
       <c r="Q37">
-        <v>2.385231275</v>
+        <v>2.35788074</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1760041724212718</v>
+        <v>0.177676315046545</v>
       </c>
       <c r="T37">
-        <v>1.259173860070456</v>
+        <v>1.275344757246019</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.279924062075673</v>
+        <v>2.216592838129126</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1341788416297888</v>
+        <v>0.1340574711857509</v>
       </c>
       <c r="C38">
-        <v>33.20519531170997</v>
+        <v>32.79147227121986</v>
       </c>
       <c r="D38">
-        <v>48.99479531170996</v>
+        <v>49.06217227121986</v>
       </c>
       <c r="E38">
-        <v>16.0096</v>
+        <v>16.4907</v>
       </c>
       <c r="F38">
-        <v>17.3196</v>
+        <v>17.8007</v>
       </c>
       <c r="G38">
         <v>1.53</v>
@@ -4403,28 +4403,28 @@
         <v>2.91</v>
       </c>
       <c r="M38">
-        <v>1.31282568</v>
+        <v>1.34929306</v>
       </c>
       <c r="N38">
-        <v>1.59717432</v>
+        <v>1.56070694</v>
       </c>
       <c r="O38">
-        <v>0.39929358</v>
+        <v>0.3901767350000001</v>
       </c>
       <c r="P38">
-        <v>1.19788074</v>
+        <v>1.170530205</v>
       </c>
       <c r="Q38">
-        <v>2.35788074</v>
+        <v>2.330530205000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.177676315046545</v>
+        <v>0.179401541564684</v>
       </c>
       <c r="T38">
-        <v>1.275344757246019</v>
+        <v>1.292029016236678</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.216592838129126</v>
+        <v>2.156684923585096</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1340574711857509</v>
+        <v>0.133936100741713</v>
       </c>
       <c r="C39">
-        <v>32.79147227121986</v>
+        <v>32.37793479762968</v>
       </c>
       <c r="D39">
-        <v>49.06217227121986</v>
+        <v>49.12973479762968</v>
       </c>
       <c r="E39">
-        <v>16.4907</v>
+        <v>16.9718</v>
       </c>
       <c r="F39">
-        <v>17.8007</v>
+        <v>18.2818</v>
       </c>
       <c r="G39">
         <v>1.53</v>
@@ -4485,28 +4485,28 @@
         <v>2.91</v>
       </c>
       <c r="M39">
-        <v>1.34929306</v>
+        <v>1.38576044</v>
       </c>
       <c r="N39">
-        <v>1.56070694</v>
+        <v>1.52423956</v>
       </c>
       <c r="O39">
-        <v>0.3901767350000001</v>
+        <v>0.38105989</v>
       </c>
       <c r="P39">
-        <v>1.170530205</v>
+        <v>1.14317967</v>
       </c>
       <c r="Q39">
-        <v>2.330530205000001</v>
+        <v>2.30317967</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.179401541564684</v>
+        <v>0.1811824205511501</v>
       </c>
       <c r="T39">
-        <v>1.292029016236678</v>
+        <v>1.309251477130262</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.156684923585096</v>
+        <v>2.099930057174961</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.133936100741713</v>
+        <v>0.1338147302976752</v>
       </c>
       <c r="C40">
-        <v>32.37793479762968</v>
+        <v>31.96458365861787</v>
       </c>
       <c r="D40">
-        <v>49.12973479762968</v>
+        <v>49.19748365861787</v>
       </c>
       <c r="E40">
-        <v>16.9718</v>
+        <v>17.4529</v>
       </c>
       <c r="F40">
-        <v>18.2818</v>
+        <v>18.7629</v>
       </c>
       <c r="G40">
         <v>1.53</v>
@@ -4567,28 +4567,28 @@
         <v>2.91</v>
       </c>
       <c r="M40">
-        <v>1.38576044</v>
+        <v>1.42222782</v>
       </c>
       <c r="N40">
-        <v>1.52423956</v>
+        <v>1.48777218</v>
       </c>
       <c r="O40">
-        <v>0.38105989</v>
+        <v>0.371943045</v>
       </c>
       <c r="P40">
-        <v>1.14317967</v>
+        <v>1.115829135</v>
       </c>
       <c r="Q40">
-        <v>2.30317967</v>
+        <v>2.275829135</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1811824205511501</v>
+        <v>0.1830216890125822</v>
       </c>
       <c r="T40">
-        <v>1.309251477130262</v>
+        <v>1.327038608872816</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.099930057174961</v>
+        <v>2.046085696734578</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1338147302976752</v>
+        <v>0.1379533598536373</v>
       </c>
       <c r="C41">
-        <v>31.96458365861787</v>
+        <v>29.27401283441892</v>
       </c>
       <c r="D41">
-        <v>49.19748365861787</v>
+        <v>46.98801283441892</v>
       </c>
       <c r="E41">
-        <v>17.4529</v>
+        <v>17.934</v>
       </c>
       <c r="F41">
-        <v>18.7629</v>
+        <v>19.244</v>
       </c>
       <c r="G41">
         <v>1.53</v>
@@ -4649,45 +4649,45 @@
         <v>2.91</v>
       </c>
       <c r="M41">
-        <v>1.42222782</v>
+        <v>1.73196</v>
       </c>
       <c r="N41">
-        <v>1.48777218</v>
+        <v>1.17804</v>
       </c>
       <c r="O41">
-        <v>0.371943045</v>
+        <v>0.29451</v>
       </c>
       <c r="P41">
-        <v>1.115829135</v>
+        <v>0.8835300000000001</v>
       </c>
       <c r="Q41">
-        <v>2.275829135</v>
+        <v>2.043530000000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1830216890125822</v>
+        <v>0.1849222664227288</v>
       </c>
       <c r="T41">
-        <v>1.327038608872816</v>
+        <v>1.345418645006789</v>
       </c>
       <c r="U41">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.046085696734578</v>
+        <v>1.680177371301878</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1379533598536373</v>
+        <v>0.1379384894095994</v>
       </c>
       <c r="C42">
-        <v>29.27401283441892</v>
+        <v>28.80049633855255</v>
       </c>
       <c r="D42">
-        <v>46.98801283441892</v>
+        <v>46.99559633855255</v>
       </c>
       <c r="E42">
-        <v>17.934</v>
+        <v>18.4151</v>
       </c>
       <c r="F42">
-        <v>19.244</v>
+        <v>19.7251</v>
       </c>
       <c r="G42">
         <v>1.53</v>
@@ -4731,28 +4731,28 @@
         <v>2.91</v>
       </c>
       <c r="M42">
-        <v>1.73196</v>
+        <v>1.775259</v>
       </c>
       <c r="N42">
-        <v>1.17804</v>
+        <v>1.134741</v>
       </c>
       <c r="O42">
-        <v>0.29451</v>
+        <v>0.28368525</v>
       </c>
       <c r="P42">
-        <v>0.8835300000000001</v>
+        <v>0.85105575</v>
       </c>
       <c r="Q42">
-        <v>2.043530000000001</v>
+        <v>2.01105575</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1849222664227288</v>
+        <v>0.1868872701857617</v>
       </c>
       <c r="T42">
-        <v>1.345418645006789</v>
+        <v>1.3644217332131</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.680177371301878</v>
+        <v>1.639197435416466</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1379384894095994</v>
+        <v>0.1379236189655615</v>
       </c>
       <c r="C43">
-        <v>28.80049633855255</v>
+        <v>28.32698229091989</v>
       </c>
       <c r="D43">
-        <v>46.99559633855255</v>
+        <v>47.0031822909199</v>
       </c>
       <c r="E43">
-        <v>18.4151</v>
+        <v>18.8962</v>
       </c>
       <c r="F43">
-        <v>19.7251</v>
+        <v>20.2062</v>
       </c>
       <c r="G43">
         <v>1.53</v>
@@ -4813,28 +4813,28 @@
         <v>2.91</v>
       </c>
       <c r="M43">
-        <v>1.775259</v>
+        <v>1.818558</v>
       </c>
       <c r="N43">
-        <v>1.134741</v>
+        <v>1.091442</v>
       </c>
       <c r="O43">
-        <v>0.28368525</v>
+        <v>0.2728605</v>
       </c>
       <c r="P43">
-        <v>0.85105575</v>
+        <v>0.8185815000000001</v>
       </c>
       <c r="Q43">
-        <v>2.01105575</v>
+        <v>1.9785815</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1868872701857617</v>
+        <v>0.188920032699244</v>
       </c>
       <c r="T43">
-        <v>1.3644217332131</v>
+        <v>1.384080100323076</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.639197435416466</v>
+        <v>1.600168925049407</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1379236189655615</v>
+        <v>0.1379087485215236</v>
       </c>
       <c r="C44">
-        <v>28.3269822909199</v>
+        <v>27.85347069270669</v>
       </c>
       <c r="D44">
-        <v>47.0031822909199</v>
+        <v>47.01077069270669</v>
       </c>
       <c r="E44">
-        <v>18.8962</v>
+        <v>19.3773</v>
       </c>
       <c r="F44">
-        <v>20.2062</v>
+        <v>20.6873</v>
       </c>
       <c r="G44">
         <v>1.53</v>
@@ -4895,28 +4895,28 @@
         <v>2.91</v>
       </c>
       <c r="M44">
-        <v>1.818558</v>
+        <v>1.861857</v>
       </c>
       <c r="N44">
-        <v>1.091442</v>
+        <v>1.048143</v>
       </c>
       <c r="O44">
-        <v>0.2728605000000001</v>
+        <v>0.2620357500000001</v>
       </c>
       <c r="P44">
-        <v>0.8185815000000002</v>
+        <v>0.7861072500000001</v>
       </c>
       <c r="Q44">
-        <v>1.9785815</v>
+        <v>1.94610725</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.188920032699244</v>
+        <v>0.1910241202131993</v>
       </c>
       <c r="T44">
-        <v>1.384080100323076</v>
+        <v>1.404428234700069</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.600168925049407</v>
+        <v>1.562955694234305</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1379087485215236</v>
+        <v>0.1378938780774857</v>
       </c>
       <c r="C45">
-        <v>27.85347069270669</v>
+        <v>27.37996154509946</v>
       </c>
       <c r="D45">
-        <v>47.01077069270669</v>
+        <v>47.01836154509945</v>
       </c>
       <c r="E45">
-        <v>19.3773</v>
+        <v>19.8584</v>
       </c>
       <c r="F45">
-        <v>20.6873</v>
+        <v>21.1684</v>
       </c>
       <c r="G45">
         <v>1.53</v>
@@ -4977,28 +4977,28 @@
         <v>2.91</v>
       </c>
       <c r="M45">
-        <v>1.861857</v>
+        <v>1.905156</v>
       </c>
       <c r="N45">
-        <v>1.048143</v>
+        <v>1.004844</v>
       </c>
       <c r="O45">
-        <v>0.2620357500000001</v>
+        <v>0.2512110000000001</v>
       </c>
       <c r="P45">
-        <v>0.7861072500000001</v>
+        <v>0.7536330000000002</v>
       </c>
       <c r="Q45">
-        <v>1.94610725</v>
+        <v>1.913633</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1910241202131993</v>
+        <v>0.193203353709796</v>
       </c>
       <c r="T45">
-        <v>1.404428234700069</v>
+        <v>1.425503088161955</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.562955694234305</v>
+        <v>1.527433973910798</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1378938780774857</v>
+        <v>0.1593227631308866</v>
       </c>
       <c r="C46">
-        <v>27.37996154509946</v>
+        <v>18.02353965227768</v>
       </c>
       <c r="D46">
-        <v>47.01836154509945</v>
+        <v>38.14303965227768</v>
       </c>
       <c r="E46">
-        <v>19.8584</v>
+        <v>20.3395</v>
       </c>
       <c r="F46">
-        <v>21.1684</v>
+        <v>21.6495</v>
       </c>
       <c r="G46">
         <v>1.53</v>
@@ -5059,45 +5059,45 @@
         <v>2.91</v>
       </c>
       <c r="M46">
-        <v>1.905156</v>
+        <v>3.1781466</v>
       </c>
       <c r="N46">
-        <v>1.004844</v>
+        <v>-0.2681466000000001</v>
       </c>
       <c r="O46">
-        <v>0.2512110000000001</v>
+        <v>-0.06703665000000003</v>
       </c>
       <c r="P46">
-        <v>0.7536330000000002</v>
+        <v>-0.2011099500000001</v>
       </c>
       <c r="Q46">
-        <v>1.913633</v>
+        <v>0.95889005</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.193203353709796</v>
+        <v>0.1970624717683699</v>
       </c>
       <c r="T46">
-        <v>1.425503088161955</v>
+        <v>1.462823709244358</v>
       </c>
       <c r="U46">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.25</v>
+        <v>0.2289069988149697</v>
       </c>
       <c r="W46">
-        <v>0.0675</v>
+        <v>0.1131964525739625</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.527433973910798</v>
+        <v>0.9156279952598788</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1593227631308866</v>
+        <v>0.1603327631308866</v>
       </c>
       <c r="C47">
-        <v>18.02353965227768</v>
+        <v>17.20607764549734</v>
       </c>
       <c r="D47">
-        <v>38.14303965227768</v>
+        <v>37.80667764549734</v>
       </c>
       <c r="E47">
-        <v>20.3395</v>
+        <v>20.8206</v>
       </c>
       <c r="F47">
-        <v>21.6495</v>
+        <v>22.1306</v>
       </c>
       <c r="G47">
         <v>1.53</v>
@@ -5141,37 +5141,37 @@
         <v>2.91</v>
       </c>
       <c r="M47">
-        <v>3.1781466</v>
+        <v>3.248772080000001</v>
       </c>
       <c r="N47">
-        <v>-0.2681466000000001</v>
+        <v>-0.3387720800000005</v>
       </c>
       <c r="O47">
-        <v>-0.06703665000000003</v>
+        <v>-0.08469302000000012</v>
       </c>
       <c r="P47">
-        <v>-0.2011099500000001</v>
+        <v>-0.2540790600000004</v>
       </c>
       <c r="Q47">
-        <v>0.95889005</v>
+        <v>0.9059209399999998</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1970624717683699</v>
+        <v>0.1998636286529694</v>
       </c>
       <c r="T47">
-        <v>1.462823709244358</v>
+        <v>1.489913037193328</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2289069988149697</v>
+        <v>0.2239307597102964</v>
       </c>
       <c r="W47">
-        <v>0.1131964525739625</v>
+        <v>0.1139269644745285</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.9156279952598788</v>
+        <v>0.8957230388411856</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1603327631308866</v>
+        <v>0.1613427631308866</v>
       </c>
       <c r="C48">
-        <v>17.20607764549734</v>
+        <v>16.39449615633047</v>
       </c>
       <c r="D48">
-        <v>37.80667764549734</v>
+        <v>37.47619615633047</v>
       </c>
       <c r="E48">
-        <v>20.8206</v>
+        <v>21.3017</v>
       </c>
       <c r="F48">
-        <v>22.1306</v>
+        <v>22.6117</v>
       </c>
       <c r="G48">
         <v>1.53</v>
@@ -5223,37 +5223,37 @@
         <v>2.91</v>
       </c>
       <c r="M48">
-        <v>3.248772080000001</v>
+        <v>3.319397560000001</v>
       </c>
       <c r="N48">
-        <v>-0.3387720800000005</v>
+        <v>-0.4093975600000004</v>
       </c>
       <c r="O48">
-        <v>-0.08469302000000012</v>
+        <v>-0.1023493900000001</v>
       </c>
       <c r="P48">
-        <v>-0.2540790600000004</v>
+        <v>-0.3070481700000003</v>
       </c>
       <c r="Q48">
-        <v>0.9059209399999998</v>
+        <v>0.8529518299999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1998636286529694</v>
+        <v>0.20277048957095</v>
       </c>
       <c r="T48">
-        <v>1.489913037193328</v>
+        <v>1.518024603932825</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2239307597102964</v>
+        <v>0.2191662754611412</v>
       </c>
       <c r="W48">
-        <v>0.1139269644745285</v>
+        <v>0.1146263907623045</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8957230388411856</v>
+        <v>0.8766651018445647</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1613427631308866</v>
+        <v>0.1623527631308866</v>
       </c>
       <c r="C49">
-        <v>16.39449615633047</v>
+        <v>15.58864231007983</v>
       </c>
       <c r="D49">
-        <v>37.47619615633047</v>
+        <v>37.15144231007983</v>
       </c>
       <c r="E49">
-        <v>21.3017</v>
+        <v>21.7828</v>
       </c>
       <c r="F49">
-        <v>22.6117</v>
+        <v>23.0928</v>
       </c>
       <c r="G49">
         <v>1.53</v>
@@ -5305,37 +5305,37 @@
         <v>2.91</v>
       </c>
       <c r="M49">
-        <v>3.319397560000001</v>
+        <v>3.39002304</v>
       </c>
       <c r="N49">
-        <v>-0.4093975600000004</v>
+        <v>-0.4800230400000003</v>
       </c>
       <c r="O49">
-        <v>-0.1023493900000001</v>
+        <v>-0.1200057600000001</v>
       </c>
       <c r="P49">
-        <v>-0.3070481700000003</v>
+        <v>-0.3600172800000002</v>
       </c>
       <c r="Q49">
-        <v>0.8529518299999999</v>
+        <v>0.7999827199999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.20277048957095</v>
+        <v>0.2057891528319298</v>
       </c>
       <c r="T49">
-        <v>1.518024603932825</v>
+        <v>1.547217384777687</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2191662754611412</v>
+        <v>0.2146003113890341</v>
       </c>
       <c r="W49">
-        <v>0.1146263907623045</v>
+        <v>0.1152966742880898</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8766651018445647</v>
+        <v>0.8584012455561363</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1623527631308866</v>
+        <v>0.1633627631308865</v>
       </c>
       <c r="C50">
-        <v>15.58864231007983</v>
+        <v>14.7883684855296</v>
       </c>
       <c r="D50">
-        <v>37.15144231007983</v>
+        <v>36.8322684855296</v>
       </c>
       <c r="E50">
-        <v>21.7828</v>
+        <v>22.2639</v>
       </c>
       <c r="F50">
-        <v>23.0928</v>
+        <v>23.5739</v>
       </c>
       <c r="G50">
         <v>1.53</v>
@@ -5387,37 +5387,37 @@
         <v>2.91</v>
       </c>
       <c r="M50">
-        <v>3.39002304</v>
+        <v>3.46064852</v>
       </c>
       <c r="N50">
-        <v>-0.4800230400000003</v>
+        <v>-0.5506485199999998</v>
       </c>
       <c r="O50">
-        <v>-0.1200057600000001</v>
+        <v>-0.1376621299999999</v>
       </c>
       <c r="P50">
-        <v>-0.3600172800000002</v>
+        <v>-0.4129863899999998</v>
       </c>
       <c r="Q50">
-        <v>0.7999827199999999</v>
+        <v>0.7470136100000003</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2057891528319298</v>
+        <v>0.2089261950443205</v>
       </c>
       <c r="T50">
-        <v>1.547217384777687</v>
+        <v>1.577554980557641</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2146003113890341</v>
+        <v>0.2102207131974212</v>
       </c>
       <c r="W50">
-        <v>0.1152966742880898</v>
+        <v>0.1159395993026186</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8584012455561363</v>
+        <v>0.8408828527896847</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1633627631308865</v>
+        <v>0.1643727631308866</v>
       </c>
       <c r="C51">
-        <v>14.7883684855296</v>
+        <v>13.99353209119996</v>
       </c>
       <c r="D51">
-        <v>36.8322684855296</v>
+        <v>36.51853209119996</v>
       </c>
       <c r="E51">
-        <v>22.2639</v>
+        <v>22.745</v>
       </c>
       <c r="F51">
-        <v>23.5739</v>
+        <v>24.055</v>
       </c>
       <c r="G51">
         <v>1.53</v>
@@ -5469,37 +5469,37 @@
         <v>2.91</v>
       </c>
       <c r="M51">
-        <v>3.46064852</v>
+        <v>3.531274</v>
       </c>
       <c r="N51">
-        <v>-0.5506485199999998</v>
+        <v>-0.6212740000000001</v>
       </c>
       <c r="O51">
-        <v>-0.1376621299999999</v>
+        <v>-0.1553185</v>
       </c>
       <c r="P51">
-        <v>-0.4129863899999998</v>
+        <v>-0.4659555000000001</v>
       </c>
       <c r="Q51">
-        <v>0.7470136100000003</v>
+        <v>0.6940445000000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2089261950443205</v>
+        <v>0.2121887189452069</v>
       </c>
       <c r="T51">
-        <v>1.577554980557641</v>
+        <v>1.609106080168794</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2102207131974212</v>
+        <v>0.2060162989334727</v>
       </c>
       <c r="W51">
-        <v>0.1159395993026186</v>
+        <v>0.1165568073165662</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8408828527896847</v>
+        <v>0.8240651957338909</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1643727631308866</v>
+        <v>0.1653827631308866</v>
       </c>
       <c r="C52">
-        <v>13.99353209119996</v>
+        <v>13.20399535294078</v>
       </c>
       <c r="D52">
-        <v>36.51853209119996</v>
+        <v>36.21009535294078</v>
       </c>
       <c r="E52">
-        <v>22.745</v>
+        <v>23.2261</v>
       </c>
       <c r="F52">
-        <v>24.055</v>
+        <v>24.5361</v>
       </c>
       <c r="G52">
         <v>1.53</v>
@@ -5551,37 +5551,37 @@
         <v>2.91</v>
       </c>
       <c r="M52">
-        <v>3.531274</v>
+        <v>3.601899480000001</v>
       </c>
       <c r="N52">
-        <v>-0.6212740000000001</v>
+        <v>-0.6918994800000005</v>
       </c>
       <c r="O52">
-        <v>-0.1553185</v>
+        <v>-0.1729748700000001</v>
       </c>
       <c r="P52">
-        <v>-0.4659555000000001</v>
+        <v>-0.5189246100000003</v>
       </c>
       <c r="Q52">
-        <v>0.6940445000000001</v>
+        <v>0.6410753899999998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2121887189452069</v>
+        <v>0.2155844070869458</v>
       </c>
       <c r="T52">
-        <v>1.609106080168794</v>
+        <v>1.641944979764076</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2060162989334727</v>
+        <v>0.2019767636602674</v>
       </c>
       <c r="W52">
-        <v>0.1165568073165662</v>
+        <v>0.1171498110946728</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8240651957338909</v>
+        <v>0.8079070546410695</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1653827631308866</v>
+        <v>0.197042017013843</v>
       </c>
       <c r="C53">
-        <v>13.20399535294078</v>
+        <v>5.143092963768158</v>
       </c>
       <c r="D53">
-        <v>36.21009535294078</v>
+        <v>28.63029296376816</v>
       </c>
       <c r="E53">
-        <v>23.2261</v>
+        <v>23.7072</v>
       </c>
       <c r="F53">
-        <v>24.5361</v>
+        <v>25.0172</v>
       </c>
       <c r="G53">
         <v>1.53</v>
@@ -5633,45 +5633,45 @@
         <v>2.91</v>
       </c>
       <c r="M53">
-        <v>3.601899480000001</v>
+        <v>5.02345376</v>
       </c>
       <c r="N53">
-        <v>-0.6918994800000005</v>
+        <v>-2.11345376</v>
       </c>
       <c r="O53">
-        <v>-0.1729748700000001</v>
+        <v>-0.5283634399999999</v>
       </c>
       <c r="P53">
-        <v>-0.5189246100000003</v>
+        <v>-1.58509032</v>
       </c>
       <c r="Q53">
-        <v>0.6410753899999998</v>
+        <v>-0.4250903199999996</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2155844070869458</v>
+        <v>0.2244741944907498</v>
       </c>
       <c r="T53">
-        <v>1.641944979764076</v>
+        <v>1.727916018266869</v>
       </c>
       <c r="U53">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.2019767636602674</v>
+        <v>0.1448206820958177</v>
       </c>
       <c r="W53">
-        <v>0.1171498110946728</v>
+        <v>0.1717200070351598</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.8079070546410695</v>
+        <v>0.5792827283832708</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.197042017013843</v>
+        <v>0.198592017013843</v>
       </c>
       <c r="C54">
-        <v>5.143092963768158</v>
+        <v>4.371552697574018</v>
       </c>
       <c r="D54">
-        <v>28.63029296376816</v>
+        <v>28.33985269757402</v>
       </c>
       <c r="E54">
-        <v>23.7072</v>
+        <v>24.1883</v>
       </c>
       <c r="F54">
-        <v>25.0172</v>
+        <v>25.4983</v>
       </c>
       <c r="G54">
         <v>1.53</v>
@@ -5715,37 +5715,37 @@
         <v>2.91</v>
       </c>
       <c r="M54">
-        <v>5.02345376</v>
+        <v>5.12005864</v>
       </c>
       <c r="N54">
-        <v>-2.11345376</v>
+        <v>-2.21005864</v>
       </c>
       <c r="O54">
-        <v>-0.5283634399999999</v>
+        <v>-0.5525146599999999</v>
       </c>
       <c r="P54">
-        <v>-1.58509032</v>
+        <v>-1.65754398</v>
       </c>
       <c r="Q54">
-        <v>-0.4250903199999996</v>
+        <v>-0.4975439799999997</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2244741944907498</v>
+        <v>0.2282757730969359</v>
       </c>
       <c r="T54">
-        <v>1.727916018266869</v>
+        <v>1.764680188868292</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1448206820958177</v>
+        <v>0.1420882163958966</v>
       </c>
       <c r="W54">
-        <v>0.1717200070351598</v>
+        <v>0.172268686147704</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5792827283832708</v>
+        <v>0.5683528655835863</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.198592017013843</v>
+        <v>0.200142017013843</v>
       </c>
       <c r="C55">
-        <v>4.371552697574018</v>
+        <v>3.605846000505256</v>
       </c>
       <c r="D55">
-        <v>28.33985269757402</v>
+        <v>28.05524600050526</v>
       </c>
       <c r="E55">
-        <v>24.1883</v>
+        <v>24.6694</v>
       </c>
       <c r="F55">
-        <v>25.4983</v>
+        <v>25.9794</v>
       </c>
       <c r="G55">
         <v>1.53</v>
@@ -5797,37 +5797,37 @@
         <v>2.91</v>
       </c>
       <c r="M55">
-        <v>5.12005864</v>
+        <v>5.216663520000001</v>
       </c>
       <c r="N55">
-        <v>-2.21005864</v>
+        <v>-2.306663520000001</v>
       </c>
       <c r="O55">
-        <v>-0.5525146599999999</v>
+        <v>-0.5766658800000002</v>
       </c>
       <c r="P55">
-        <v>-1.65754398</v>
+        <v>-1.729997640000001</v>
       </c>
       <c r="Q55">
-        <v>-0.4975439799999997</v>
+        <v>-0.5699976400000004</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2282757730969359</v>
+        <v>0.232242637729478</v>
       </c>
       <c r="T55">
-        <v>1.764680188868292</v>
+        <v>1.803042801669776</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1420882163958966</v>
+        <v>0.1394569531293059</v>
       </c>
       <c r="W55">
-        <v>0.172268686147704</v>
+        <v>0.1727970438116354</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5683528655835863</v>
+        <v>0.5578278125172236</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.200142017013843</v>
+        <v>0.201692017013843</v>
       </c>
       <c r="C56">
-        <v>3.605846000505256</v>
+        <v>2.845798866881847</v>
       </c>
       <c r="D56">
-        <v>28.05524600050526</v>
+        <v>27.77629886688185</v>
       </c>
       <c r="E56">
-        <v>24.6694</v>
+        <v>25.1505</v>
       </c>
       <c r="F56">
-        <v>25.9794</v>
+        <v>26.4605</v>
       </c>
       <c r="G56">
         <v>1.53</v>
@@ -5879,37 +5879,37 @@
         <v>2.91</v>
       </c>
       <c r="M56">
-        <v>5.216663520000001</v>
+        <v>5.313268400000001</v>
       </c>
       <c r="N56">
-        <v>-2.306663520000001</v>
+        <v>-2.403268400000001</v>
       </c>
       <c r="O56">
-        <v>-0.5766658800000002</v>
+        <v>-0.6008171000000002</v>
       </c>
       <c r="P56">
-        <v>-1.729997640000001</v>
+        <v>-1.802451300000001</v>
       </c>
       <c r="Q56">
-        <v>-0.5699976400000004</v>
+        <v>-0.6424513000000005</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.232242637729478</v>
+        <v>0.2363858074567998</v>
       </c>
       <c r="T56">
-        <v>1.803042801669776</v>
+        <v>1.84311041948466</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1394569531293059</v>
+        <v>0.1369213721633185</v>
       </c>
       <c r="W56">
-        <v>0.1727970438116354</v>
+        <v>0.1733061884696057</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5578278125172236</v>
+        <v>0.547685488653274</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.201692017013843</v>
+        <v>0.203242017013843</v>
       </c>
       <c r="C57">
-        <v>2.845798866881847</v>
+        <v>2.091244143293785</v>
       </c>
       <c r="D57">
-        <v>27.77629886688185</v>
+        <v>27.50284414329379</v>
       </c>
       <c r="E57">
-        <v>25.1505</v>
+        <v>25.6316</v>
       </c>
       <c r="F57">
-        <v>26.4605</v>
+        <v>26.9416</v>
       </c>
       <c r="G57">
         <v>1.53</v>
@@ -5961,37 +5961,37 @@
         <v>2.91</v>
       </c>
       <c r="M57">
-        <v>5.313268400000001</v>
+        <v>5.40987328</v>
       </c>
       <c r="N57">
-        <v>-2.403268400000001</v>
+        <v>-2.49987328</v>
       </c>
       <c r="O57">
-        <v>-0.6008171000000002</v>
+        <v>-0.62496832</v>
       </c>
       <c r="P57">
-        <v>-1.802451300000001</v>
+        <v>-1.87490496</v>
       </c>
       <c r="Q57">
-        <v>-0.6424513000000005</v>
+        <v>-0.7149049599999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2363858074567998</v>
+        <v>0.240717303080818</v>
       </c>
       <c r="T57">
-        <v>1.84311041948466</v>
+        <v>1.884999292654767</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1369213721633185</v>
+        <v>0.1344763476604021</v>
       </c>
       <c r="W57">
-        <v>0.1733061884696057</v>
+        <v>0.1737971493897913</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.547685488653274</v>
+        <v>0.5379053906416085</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.203242017013843</v>
+        <v>0.204792017013843</v>
       </c>
       <c r="C58">
-        <v>2.091244143293785</v>
+        <v>1.342021194590053</v>
       </c>
       <c r="D58">
-        <v>27.50284414329379</v>
+        <v>27.23472119459005</v>
       </c>
       <c r="E58">
-        <v>25.6316</v>
+        <v>26.1127</v>
       </c>
       <c r="F58">
-        <v>26.9416</v>
+        <v>27.4227</v>
       </c>
       <c r="G58">
         <v>1.53</v>
@@ -6043,37 +6043,37 @@
         <v>2.91</v>
       </c>
       <c r="M58">
-        <v>5.40987328</v>
+        <v>5.50647816</v>
       </c>
       <c r="N58">
-        <v>-2.49987328</v>
+        <v>-2.59647816</v>
       </c>
       <c r="O58">
-        <v>-0.62496832</v>
+        <v>-0.6491195400000001</v>
       </c>
       <c r="P58">
-        <v>-1.87490496</v>
+        <v>-1.94735862</v>
       </c>
       <c r="Q58">
-        <v>-0.7149049599999999</v>
+        <v>-0.78735862</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.240717303080818</v>
+        <v>0.2452502636175812</v>
       </c>
       <c r="T58">
-        <v>1.884999292654767</v>
+        <v>1.928836485507203</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1344763476604021</v>
+        <v>0.1321171134909214</v>
       </c>
       <c r="W58">
-        <v>0.1737971493897913</v>
+        <v>0.174270883611023</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5379053906416085</v>
+        <v>0.5284684539636856</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.204792017013843</v>
+        <v>0.206342017013843</v>
       </c>
       <c r="C59">
-        <v>1.342021194590053</v>
+        <v>0.5979755892163858</v>
       </c>
       <c r="D59">
-        <v>27.23472119459005</v>
+        <v>26.97177558921639</v>
       </c>
       <c r="E59">
-        <v>26.1127</v>
+        <v>26.59380000000001</v>
       </c>
       <c r="F59">
-        <v>27.4227</v>
+        <v>27.9038</v>
       </c>
       <c r="G59">
         <v>1.53</v>
@@ -6125,37 +6125,37 @@
         <v>2.91</v>
       </c>
       <c r="M59">
-        <v>5.50647816</v>
+        <v>5.603083040000001</v>
       </c>
       <c r="N59">
-        <v>-2.59647816</v>
+        <v>-2.693083040000001</v>
       </c>
       <c r="O59">
-        <v>-0.6491195400000001</v>
+        <v>-0.6732707600000003</v>
       </c>
       <c r="P59">
-        <v>-1.94735862</v>
+        <v>-2.019812280000001</v>
       </c>
       <c r="Q59">
-        <v>-0.78735862</v>
+        <v>-0.8598122800000008</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2452502636175812</v>
+        <v>0.2499990794179998</v>
       </c>
       <c r="T59">
-        <v>1.928836485507203</v>
+        <v>1.974761163733565</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1321171134909214</v>
+        <v>0.1298392322238365</v>
       </c>
       <c r="W59">
-        <v>0.174270883611023</v>
+        <v>0.1747282821694536</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5284684539636856</v>
+        <v>0.5193569288953461</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.206342017013843</v>
+        <v>0.207892017013843</v>
       </c>
       <c r="C60">
-        <v>0.5979755892164</v>
+        <v>-0.1410411973932426</v>
       </c>
       <c r="D60">
-        <v>26.9717755892164</v>
+        <v>26.71385880260675</v>
       </c>
       <c r="E60">
-        <v>26.5938</v>
+        <v>27.0749</v>
       </c>
       <c r="F60">
-        <v>27.9038</v>
+        <v>28.3849</v>
       </c>
       <c r="G60">
         <v>1.53</v>
@@ -6207,37 +6207,37 @@
         <v>2.91</v>
       </c>
       <c r="M60">
-        <v>5.60308304</v>
+        <v>5.69968792</v>
       </c>
       <c r="N60">
-        <v>-2.693083039999999</v>
+        <v>-2.78968792</v>
       </c>
       <c r="O60">
-        <v>-0.6732707599999999</v>
+        <v>-0.6974219799999999</v>
       </c>
       <c r="P60">
-        <v>-2.01981228</v>
+        <v>-2.09226594</v>
       </c>
       <c r="Q60">
-        <v>-0.8598122799999994</v>
+        <v>-0.9322659399999997</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2499990794179997</v>
+        <v>0.2549795447696582</v>
       </c>
       <c r="T60">
-        <v>1.974761163733564</v>
+        <v>2.02292607016609</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1298392322238366</v>
+        <v>0.1276385672708902</v>
       </c>
       <c r="W60">
-        <v>0.1747282821694536</v>
+        <v>0.1751701756920053</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5193569288953462</v>
+        <v>0.5105542690835607</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.207892017013843</v>
+        <v>0.209442017013843</v>
       </c>
       <c r="C61">
-        <v>-0.1410411973932426</v>
+        <v>-0.8751720625685202</v>
       </c>
       <c r="D61">
-        <v>26.71385880260675</v>
+        <v>26.46082793743148</v>
       </c>
       <c r="E61">
-        <v>27.0749</v>
+        <v>27.556</v>
       </c>
       <c r="F61">
-        <v>28.3849</v>
+        <v>28.866</v>
       </c>
       <c r="G61">
         <v>1.53</v>
@@ -6289,37 +6289,37 @@
         <v>2.91</v>
       </c>
       <c r="M61">
-        <v>5.69968792</v>
+        <v>5.7962928</v>
       </c>
       <c r="N61">
-        <v>-2.78968792</v>
+        <v>-2.8862928</v>
       </c>
       <c r="O61">
-        <v>-0.6974219799999999</v>
+        <v>-0.7215731999999999</v>
       </c>
       <c r="P61">
-        <v>-2.09226594</v>
+        <v>-2.1647196</v>
       </c>
       <c r="Q61">
-        <v>-0.9322659399999997</v>
+        <v>-1.0047196</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2549795447696582</v>
+        <v>0.2602090333888997</v>
       </c>
       <c r="T61">
-        <v>2.02292607016609</v>
+        <v>2.073499221920243</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1276385672708902</v>
+        <v>0.1255112578163753</v>
       </c>
       <c r="W61">
-        <v>0.1751701756920053</v>
+        <v>0.1755973394304718</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5105542690835607</v>
+        <v>0.5020450312655014</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.209442017013843</v>
+        <v>0.2333787419887614</v>
       </c>
       <c r="C62">
-        <v>-0.8751720625685202</v>
+        <v>-4.732910343813003</v>
       </c>
       <c r="D62">
-        <v>26.46082793743148</v>
+        <v>23.08418965618699</v>
       </c>
       <c r="E62">
-        <v>27.556</v>
+        <v>28.0371</v>
       </c>
       <c r="F62">
-        <v>28.866</v>
+        <v>29.3471</v>
       </c>
       <c r="G62">
         <v>1.53</v>
@@ -6371,45 +6371,45 @@
         <v>2.91</v>
       </c>
       <c r="M62">
-        <v>5.7962928</v>
+        <v>6.92004618</v>
       </c>
       <c r="N62">
-        <v>-2.8862928</v>
+        <v>-4.01004618</v>
       </c>
       <c r="O62">
-        <v>-0.7215731999999999</v>
+        <v>-1.002511545</v>
       </c>
       <c r="P62">
-        <v>-2.1647196</v>
+        <v>-3.007534635</v>
       </c>
       <c r="Q62">
-        <v>-1.0047196</v>
+        <v>-1.847534635</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2602090333888997</v>
+        <v>0.2683649700781493</v>
       </c>
       <c r="T62">
-        <v>2.073499221920243</v>
+        <v>2.152373363144114</v>
       </c>
       <c r="U62">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1255112578163753</v>
+        <v>0.1051293562321285</v>
       </c>
       <c r="W62">
-        <v>0.1755973394304718</v>
+        <v>0.2110104978004641</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.5020450312655014</v>
+        <v>0.420517424928514</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2333787419887614</v>
+        <v>0.2352787419887613</v>
       </c>
       <c r="C63">
-        <v>-4.732910343813003</v>
+        <v>-5.445487288859198</v>
       </c>
       <c r="D63">
-        <v>23.08418965618699</v>
+        <v>22.8527127111408</v>
       </c>
       <c r="E63">
-        <v>28.0371</v>
+        <v>28.5182</v>
       </c>
       <c r="F63">
-        <v>29.3471</v>
+        <v>29.8282</v>
       </c>
       <c r="G63">
         <v>1.53</v>
@@ -6453,37 +6453,37 @@
         <v>2.91</v>
       </c>
       <c r="M63">
-        <v>6.92004618</v>
+        <v>7.03348956</v>
       </c>
       <c r="N63">
-        <v>-4.01004618</v>
+        <v>-4.12348956</v>
       </c>
       <c r="O63">
-        <v>-1.002511545</v>
+        <v>-1.03087239</v>
       </c>
       <c r="P63">
-        <v>-3.007534635</v>
+        <v>-3.09261717</v>
       </c>
       <c r="Q63">
-        <v>-1.847534635</v>
+        <v>-1.93261717</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2683649700781493</v>
+        <v>0.2742219429749427</v>
       </c>
       <c r="T63">
-        <v>2.152373363144114</v>
+        <v>2.20901476743738</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1051293562321285</v>
+        <v>0.1034337214541909</v>
       </c>
       <c r="W63">
-        <v>0.2110104978004641</v>
+        <v>0.2114103284811018</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.420517424928514</v>
+        <v>0.4137348858167638</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2352787419887613</v>
+        <v>0.2371787419887613</v>
       </c>
       <c r="C64">
-        <v>-5.445487288859198</v>
+        <v>-6.153468047400903</v>
       </c>
       <c r="D64">
-        <v>22.8527127111408</v>
+        <v>22.6258319525991</v>
       </c>
       <c r="E64">
-        <v>28.5182</v>
+        <v>28.9993</v>
       </c>
       <c r="F64">
-        <v>29.8282</v>
+        <v>30.3093</v>
       </c>
       <c r="G64">
         <v>1.53</v>
@@ -6535,37 +6535,37 @@
         <v>2.91</v>
       </c>
       <c r="M64">
-        <v>7.03348956</v>
+        <v>7.14693294</v>
       </c>
       <c r="N64">
-        <v>-4.12348956</v>
+        <v>-4.23693294</v>
       </c>
       <c r="O64">
-        <v>-1.03087239</v>
+        <v>-1.059233235</v>
       </c>
       <c r="P64">
-        <v>-3.09261717</v>
+        <v>-3.177699705</v>
       </c>
       <c r="Q64">
-        <v>-1.93261717</v>
+        <v>-2.017699705</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2742219429749427</v>
+        <v>0.2803955090012924</v>
       </c>
       <c r="T64">
-        <v>2.20901476743738</v>
+        <v>2.268717869260011</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1034337214541909</v>
+        <v>0.1017919163517435</v>
       </c>
       <c r="W64">
-        <v>0.2114103284811018</v>
+        <v>0.2117974661242589</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4137348858167638</v>
+        <v>0.4071676654069739</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2371787419887613</v>
+        <v>0.2390787419887613</v>
       </c>
       <c r="C65">
-        <v>-6.153468047400903</v>
+        <v>-6.85698816596955</v>
       </c>
       <c r="D65">
-        <v>22.6258319525991</v>
+        <v>22.40341183403045</v>
       </c>
       <c r="E65">
-        <v>28.9993</v>
+        <v>29.4804</v>
       </c>
       <c r="F65">
-        <v>30.3093</v>
+        <v>30.7904</v>
       </c>
       <c r="G65">
         <v>1.53</v>
@@ -6617,37 +6617,37 @@
         <v>2.91</v>
       </c>
       <c r="M65">
-        <v>7.14693294</v>
+        <v>7.260376320000001</v>
       </c>
       <c r="N65">
-        <v>-4.23693294</v>
+        <v>-4.350376320000001</v>
       </c>
       <c r="O65">
-        <v>-1.059233235</v>
+        <v>-1.08759408</v>
       </c>
       <c r="P65">
-        <v>-3.177699705</v>
+        <v>-3.26278224</v>
       </c>
       <c r="Q65">
-        <v>-2.017699705</v>
+        <v>-2.10278224</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2803955090012924</v>
+        <v>0.286912050917995</v>
       </c>
       <c r="T65">
-        <v>2.268717869260011</v>
+        <v>2.33173781007279</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1017919163517435</v>
+        <v>0.1002014176587475</v>
       </c>
       <c r="W65">
-        <v>0.2117974661242589</v>
+        <v>0.2121725057160674</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4071676654069739</v>
+        <v>0.4008056706349898</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2390787419887613</v>
+        <v>0.2409787419887613</v>
       </c>
       <c r="C66">
-        <v>-6.85698816596955</v>
+        <v>-7.556177913095333</v>
       </c>
       <c r="D66">
-        <v>22.40341183403045</v>
+        <v>22.18532208690467</v>
       </c>
       <c r="E66">
-        <v>29.4804</v>
+        <v>29.9615</v>
       </c>
       <c r="F66">
-        <v>30.7904</v>
+        <v>31.2715</v>
       </c>
       <c r="G66">
         <v>1.53</v>
@@ -6699,37 +6699,37 @@
         <v>2.91</v>
       </c>
       <c r="M66">
-        <v>7.260376320000001</v>
+        <v>7.3738197</v>
       </c>
       <c r="N66">
-        <v>-4.350376320000001</v>
+        <v>-4.4638197</v>
       </c>
       <c r="O66">
-        <v>-1.08759408</v>
+        <v>-1.115954925</v>
       </c>
       <c r="P66">
-        <v>-3.26278224</v>
+        <v>-3.347864775</v>
       </c>
       <c r="Q66">
-        <v>-2.10278224</v>
+        <v>-2.187864775</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.286912050917995</v>
+        <v>0.2938009666585092</v>
       </c>
       <c r="T66">
-        <v>2.33173781007279</v>
+        <v>2.398358890360584</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1002014176587475</v>
+        <v>0.09865985738707443</v>
       </c>
       <c r="W66">
-        <v>0.2121725057160674</v>
+        <v>0.2125360056281279</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4008056706349898</v>
+        <v>0.3946394295482978</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2409787419887613</v>
+        <v>0.2428787419887613</v>
       </c>
       <c r="C67">
-        <v>-7.556177913095333</v>
+        <v>-8.251162533728458</v>
       </c>
       <c r="D67">
-        <v>22.18532208690467</v>
+        <v>21.97143746627154</v>
       </c>
       <c r="E67">
-        <v>29.9615</v>
+        <v>30.4426</v>
       </c>
       <c r="F67">
-        <v>31.2715</v>
+        <v>31.7526</v>
       </c>
       <c r="G67">
         <v>1.53</v>
@@ -6781,37 +6781,37 @@
         <v>2.91</v>
       </c>
       <c r="M67">
-        <v>7.3738197</v>
+        <v>7.487263080000001</v>
       </c>
       <c r="N67">
-        <v>-4.4638197</v>
+        <v>-4.577263080000001</v>
       </c>
       <c r="O67">
-        <v>-1.115954925</v>
+        <v>-1.14431577</v>
       </c>
       <c r="P67">
-        <v>-3.347864775</v>
+        <v>-3.43294731</v>
       </c>
       <c r="Q67">
-        <v>-2.187864775</v>
+        <v>-2.27294731</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2938009666585092</v>
+        <v>0.3010951127367006</v>
       </c>
       <c r="T67">
-        <v>2.398358890360584</v>
+        <v>2.46889885772413</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09865985738707443</v>
+        <v>0.09716501106302784</v>
       </c>
       <c r="W67">
-        <v>0.2125360056281279</v>
+        <v>0.212888490391338</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3946394295482978</v>
+        <v>0.3886600442521114</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2428787419887613</v>
+        <v>0.2447787419887613</v>
       </c>
       <c r="C68">
-        <v>-8.251162533728458</v>
+        <v>-8.942062489083856</v>
       </c>
       <c r="D68">
-        <v>21.97143746627154</v>
+        <v>21.76163751091614</v>
       </c>
       <c r="E68">
-        <v>30.4426</v>
+        <v>30.9237</v>
       </c>
       <c r="F68">
-        <v>31.7526</v>
+        <v>32.2337</v>
       </c>
       <c r="G68">
         <v>1.53</v>
@@ -6863,37 +6863,37 @@
         <v>2.91</v>
       </c>
       <c r="M68">
-        <v>7.487263080000001</v>
+        <v>7.60070646</v>
       </c>
       <c r="N68">
-        <v>-4.577263080000001</v>
+        <v>-4.690706459999999</v>
       </c>
       <c r="O68">
-        <v>-1.14431577</v>
+        <v>-1.172676615</v>
       </c>
       <c r="P68">
-        <v>-3.43294731</v>
+        <v>-3.518029845</v>
       </c>
       <c r="Q68">
-        <v>-2.27294731</v>
+        <v>-2.358029844999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3010951127367006</v>
+        <v>0.3088313282741764</v>
       </c>
       <c r="T68">
-        <v>2.46889885772413</v>
+        <v>2.543713974624862</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09716501106302784</v>
+        <v>0.09571478701731102</v>
       </c>
       <c r="W68">
-        <v>0.212888490391338</v>
+        <v>0.2132304532213181</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3886600442521114</v>
+        <v>0.3828591480692441</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2447787419887613</v>
+        <v>0.2466787419887613</v>
       </c>
       <c r="C69">
-        <v>-8.942062489083856</v>
+        <v>-9.628993682874658</v>
       </c>
       <c r="D69">
-        <v>21.76163751091614</v>
+        <v>21.55580631712535</v>
       </c>
       <c r="E69">
-        <v>30.9237</v>
+        <v>31.40480000000001</v>
       </c>
       <c r="F69">
-        <v>32.2337</v>
+        <v>32.7148</v>
       </c>
       <c r="G69">
         <v>1.53</v>
@@ -6945,37 +6945,37 @@
         <v>2.91</v>
       </c>
       <c r="M69">
-        <v>7.60070646</v>
+        <v>7.714149840000001</v>
       </c>
       <c r="N69">
-        <v>-4.690706459999999</v>
+        <v>-4.804149840000001</v>
       </c>
       <c r="O69">
-        <v>-1.172676615</v>
+        <v>-1.20103746</v>
       </c>
       <c r="P69">
-        <v>-3.518029845</v>
+        <v>-3.603112380000001</v>
       </c>
       <c r="Q69">
-        <v>-2.358029844999999</v>
+        <v>-2.443112380000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3088313282741764</v>
+        <v>0.3170510572827445</v>
       </c>
       <c r="T69">
-        <v>2.543713974624862</v>
+        <v>2.623205036331889</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09571478701731102</v>
+        <v>0.09430721661999761</v>
       </c>
       <c r="W69">
-        <v>0.2132304532213181</v>
+        <v>0.2135623583210046</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3828591480692441</v>
+        <v>0.3772288664799904</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2466787419887613</v>
+        <v>0.2485787419887613</v>
       </c>
       <c r="C70">
-        <v>-9.628993682874658</v>
+        <v>-10.31206767482698</v>
       </c>
       <c r="D70">
-        <v>21.55580631712535</v>
+        <v>21.35383232517302</v>
       </c>
       <c r="E70">
-        <v>31.40480000000001</v>
+        <v>31.8859</v>
       </c>
       <c r="F70">
-        <v>32.7148</v>
+        <v>33.1959</v>
       </c>
       <c r="G70">
         <v>1.53</v>
@@ -7027,37 +7027,37 @@
         <v>2.91</v>
       </c>
       <c r="M70">
-        <v>7.714149840000001</v>
+        <v>7.827593220000001</v>
       </c>
       <c r="N70">
-        <v>-4.804149840000001</v>
+        <v>-4.917593220000001</v>
       </c>
       <c r="O70">
-        <v>-1.20103746</v>
+        <v>-1.229398305</v>
       </c>
       <c r="P70">
-        <v>-3.603112380000001</v>
+        <v>-3.688194915</v>
       </c>
       <c r="Q70">
-        <v>-2.443112380000001</v>
+        <v>-2.528194915</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3170510572827445</v>
+        <v>0.3258010913886395</v>
       </c>
       <c r="T70">
-        <v>2.623205036331889</v>
+        <v>2.707824553632918</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09430721661999761</v>
+        <v>0.09294044536463533</v>
       </c>
       <c r="W70">
-        <v>0.2135623583210046</v>
+        <v>0.213884642983019</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3772288664799904</v>
+        <v>0.3717617814585413</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2485787419887613</v>
+        <v>0.2504787419887613</v>
       </c>
       <c r="C71">
-        <v>-10.31206767482698</v>
+        <v>-10.99139188230258</v>
       </c>
       <c r="D71">
-        <v>21.35383232517302</v>
+        <v>21.15560811769742</v>
       </c>
       <c r="E71">
-        <v>31.8859</v>
+        <v>32.367</v>
       </c>
       <c r="F71">
-        <v>33.1959</v>
+        <v>33.677</v>
       </c>
       <c r="G71">
         <v>1.53</v>
@@ -7109,37 +7109,37 @@
         <v>2.91</v>
       </c>
       <c r="M71">
-        <v>7.827593220000001</v>
+        <v>7.9410366</v>
       </c>
       <c r="N71">
-        <v>-4.917593220000001</v>
+        <v>-5.0310366</v>
       </c>
       <c r="O71">
-        <v>-1.229398305</v>
+        <v>-1.25775915</v>
       </c>
       <c r="P71">
-        <v>-3.688194915</v>
+        <v>-3.77327745</v>
       </c>
       <c r="Q71">
-        <v>-2.528194915</v>
+        <v>-2.61327745</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3258010913886395</v>
+        <v>0.3351344611015941</v>
       </c>
       <c r="T71">
-        <v>2.707824553632918</v>
+        <v>2.798085372087348</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09294044536463533</v>
+        <v>0.09161272471656912</v>
       </c>
       <c r="W71">
-        <v>0.213884642983019</v>
+        <v>0.214197719511833</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3717617814585413</v>
+        <v>0.3664508988662765</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2504787419887613</v>
+        <v>0.2523787419887614</v>
       </c>
       <c r="C72">
-        <v>-10.99139188230258</v>
+        <v>-11.66706977079517</v>
       </c>
       <c r="D72">
-        <v>21.15560811769742</v>
+        <v>20.96103022920484</v>
       </c>
       <c r="E72">
-        <v>32.367</v>
+        <v>32.8481</v>
       </c>
       <c r="F72">
-        <v>33.677</v>
+        <v>34.1581</v>
       </c>
       <c r="G72">
         <v>1.53</v>
@@ -7191,37 +7191,37 @@
         <v>2.91</v>
       </c>
       <c r="M72">
-        <v>7.9410366</v>
+        <v>8.054479980000002</v>
       </c>
       <c r="N72">
-        <v>-5.0310366</v>
+        <v>-5.144479980000002</v>
       </c>
       <c r="O72">
-        <v>-1.25775915</v>
+        <v>-1.286119995</v>
       </c>
       <c r="P72">
-        <v>-3.77327745</v>
+        <v>-3.858359985000001</v>
       </c>
       <c r="Q72">
-        <v>-2.61327745</v>
+        <v>-2.698359985000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3351344611015941</v>
+        <v>0.3451115114844077</v>
       </c>
       <c r="T72">
-        <v>2.798085372087348</v>
+        <v>2.894571074573119</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09161272471656912</v>
+        <v>0.09032240465013855</v>
       </c>
       <c r="W72">
-        <v>0.214197719511833</v>
+        <v>0.2145019769834973</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3664508988662765</v>
+        <v>0.3612896186005542</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2523787419887613</v>
+        <v>0.2542787419887613</v>
       </c>
       <c r="C73">
-        <v>-11.66706977079516</v>
+        <v>-12.33920103400969</v>
       </c>
       <c r="D73">
-        <v>20.96103022920484</v>
+        <v>20.7699989659903</v>
       </c>
       <c r="E73">
-        <v>32.8481</v>
+        <v>33.32919999999999</v>
       </c>
       <c r="F73">
-        <v>34.1581</v>
+        <v>34.6392</v>
       </c>
       <c r="G73">
         <v>1.53</v>
@@ -7273,37 +7273,37 @@
         <v>2.91</v>
       </c>
       <c r="M73">
-        <v>8.05447998</v>
+        <v>8.16792336</v>
       </c>
       <c r="N73">
-        <v>-5.14447998</v>
+        <v>-5.257923359999999</v>
       </c>
       <c r="O73">
-        <v>-1.286119995</v>
+        <v>-1.31448084</v>
       </c>
       <c r="P73">
-        <v>-3.858359985</v>
+        <v>-3.94344252</v>
       </c>
       <c r="Q73">
-        <v>-2.698359985</v>
+        <v>-2.783442519999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3451115114844076</v>
+        <v>0.3558012083231364</v>
       </c>
       <c r="T73">
-        <v>2.894571074573118</v>
+        <v>2.997948612950729</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09032240465013858</v>
+        <v>0.08906792680777555</v>
       </c>
       <c r="W73">
-        <v>0.2145019769834973</v>
+        <v>0.2147977828587265</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3612896186005543</v>
+        <v>0.3562717072311021</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2542787419887613</v>
+        <v>0.2561787419887613</v>
       </c>
       <c r="C74">
-        <v>-12.33920103400969</v>
+        <v>-13.00788176418389</v>
       </c>
       <c r="D74">
-        <v>20.7699989659903</v>
+        <v>20.58241823581611</v>
       </c>
       <c r="E74">
-        <v>33.32919999999999</v>
+        <v>33.8103</v>
       </c>
       <c r="F74">
-        <v>34.6392</v>
+        <v>35.1203</v>
       </c>
       <c r="G74">
         <v>1.53</v>
@@ -7355,37 +7355,37 @@
         <v>2.91</v>
       </c>
       <c r="M74">
-        <v>8.16792336</v>
+        <v>8.281366740000001</v>
       </c>
       <c r="N74">
-        <v>-5.257923359999999</v>
+        <v>-5.371366740000001</v>
       </c>
       <c r="O74">
-        <v>-1.31448084</v>
+        <v>-1.342841685</v>
       </c>
       <c r="P74">
-        <v>-3.94344252</v>
+        <v>-4.028525055000001</v>
       </c>
       <c r="Q74">
-        <v>-2.783442519999999</v>
+        <v>-2.868525055000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3558012083231364</v>
+        <v>0.3672827345573267</v>
       </c>
       <c r="T74">
-        <v>2.997948612950729</v>
+        <v>3.108983746763719</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08906792680777555</v>
+        <v>0.08784781822136764</v>
       </c>
       <c r="W74">
-        <v>0.2147977828587265</v>
+        <v>0.2150854844634015</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3562717072311021</v>
+        <v>0.3513912728854706</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2561787419887613</v>
+        <v>0.2580787419887614</v>
       </c>
       <c r="C75">
-        <v>-13.00788176418389</v>
+        <v>-13.67320461326278</v>
       </c>
       <c r="D75">
-        <v>20.58241823581611</v>
+        <v>20.39819538673722</v>
       </c>
       <c r="E75">
-        <v>33.8103</v>
+        <v>34.2914</v>
       </c>
       <c r="F75">
-        <v>35.1203</v>
+        <v>35.6014</v>
       </c>
       <c r="G75">
         <v>1.53</v>
@@ -7437,37 +7437,37 @@
         <v>2.91</v>
       </c>
       <c r="M75">
-        <v>8.281366740000001</v>
+        <v>8.394810120000001</v>
       </c>
       <c r="N75">
-        <v>-5.371366740000001</v>
+        <v>-5.484810120000001</v>
       </c>
       <c r="O75">
-        <v>-1.342841685</v>
+        <v>-1.37120253</v>
       </c>
       <c r="P75">
-        <v>-4.028525055000001</v>
+        <v>-4.113607590000001</v>
       </c>
       <c r="Q75">
-        <v>-2.868525055000001</v>
+        <v>-2.953607590000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3672827345573267</v>
+        <v>0.3796474551172239</v>
       </c>
       <c r="T75">
-        <v>3.108983746763719</v>
+        <v>3.22856004471617</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08784781822136764</v>
+        <v>0.08666068554270051</v>
       </c>
       <c r="W75">
-        <v>0.2150854844634015</v>
+        <v>0.2153654103490312</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3513912728854706</v>
+        <v>0.346642742170802</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2580787419887614</v>
+        <v>0.2599787419887614</v>
       </c>
       <c r="C76">
-        <v>-13.67320461326278</v>
+        <v>-14.33525894549447</v>
       </c>
       <c r="D76">
-        <v>20.39819538673722</v>
+        <v>20.21724105450553</v>
       </c>
       <c r="E76">
-        <v>34.2914</v>
+        <v>34.77249999999999</v>
       </c>
       <c r="F76">
-        <v>35.6014</v>
+        <v>36.0825</v>
       </c>
       <c r="G76">
         <v>1.53</v>
@@ -7519,37 +7519,37 @@
         <v>2.91</v>
       </c>
       <c r="M76">
-        <v>8.394810120000001</v>
+        <v>8.508253499999999</v>
       </c>
       <c r="N76">
-        <v>-5.484810120000001</v>
+        <v>-5.598253499999998</v>
       </c>
       <c r="O76">
-        <v>-1.37120253</v>
+        <v>-1.399563375</v>
       </c>
       <c r="P76">
-        <v>-4.113607590000001</v>
+        <v>-4.198690124999999</v>
       </c>
       <c r="Q76">
-        <v>-2.953607590000001</v>
+        <v>-3.038690124999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3796474551172239</v>
+        <v>0.3930013533219129</v>
       </c>
       <c r="T76">
-        <v>3.22856004471617</v>
+        <v>3.357702446504817</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08666068554270051</v>
+        <v>0.08550520973546454</v>
       </c>
       <c r="W76">
-        <v>0.2153654103490312</v>
+        <v>0.2156378715443775</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.346642742170802</v>
+        <v>0.3420208389418581</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2599787419887614</v>
+        <v>0.2618787419887613</v>
       </c>
       <c r="C77">
-        <v>-14.33525894549447</v>
+        <v>-14.99413098197531</v>
       </c>
       <c r="D77">
-        <v>20.21724105450553</v>
+        <v>20.03946901802469</v>
       </c>
       <c r="E77">
-        <v>34.77249999999999</v>
+        <v>35.2536</v>
       </c>
       <c r="F77">
-        <v>36.0825</v>
+        <v>36.5636</v>
       </c>
       <c r="G77">
         <v>1.53</v>
@@ -7601,37 +7601,37 @@
         <v>2.91</v>
       </c>
       <c r="M77">
-        <v>8.508253499999999</v>
+        <v>8.62169688</v>
       </c>
       <c r="N77">
-        <v>-5.598253499999998</v>
+        <v>-5.71169688</v>
       </c>
       <c r="O77">
-        <v>-1.399563375</v>
+        <v>-1.42792422</v>
       </c>
       <c r="P77">
-        <v>-4.198690124999999</v>
+        <v>-4.28377266</v>
       </c>
       <c r="Q77">
-        <v>-3.038690124999999</v>
+        <v>-3.12377266</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3930013533219129</v>
+        <v>0.4074680763769926</v>
       </c>
       <c r="T77">
-        <v>3.357702446504817</v>
+        <v>3.497606715109185</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08550520973546454</v>
+        <v>0.08438014118631366</v>
       </c>
       <c r="W77">
-        <v>0.2156378715443775</v>
+        <v>0.2159031627082673</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3420208389418581</v>
+        <v>0.3375205647452547</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2618787419887613</v>
+        <v>0.2637787419887613</v>
       </c>
       <c r="C78">
-        <v>-14.99413098197531</v>
+        <v>-15.64990393763541</v>
       </c>
       <c r="D78">
-        <v>20.03946901802469</v>
+        <v>19.86479606236459</v>
       </c>
       <c r="E78">
-        <v>35.2536</v>
+        <v>35.7347</v>
       </c>
       <c r="F78">
-        <v>36.5636</v>
+        <v>37.0447</v>
       </c>
       <c r="G78">
         <v>1.53</v>
@@ -7683,37 +7683,37 @@
         <v>2.91</v>
       </c>
       <c r="M78">
-        <v>8.62169688</v>
+        <v>8.73514026</v>
       </c>
       <c r="N78">
-        <v>-5.71169688</v>
+        <v>-5.82514026</v>
       </c>
       <c r="O78">
-        <v>-1.42792422</v>
+        <v>-1.456285065</v>
       </c>
       <c r="P78">
-        <v>-4.28377266</v>
+        <v>-4.368855195</v>
       </c>
       <c r="Q78">
-        <v>-3.12377266</v>
+        <v>-3.208855195</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4074680763769926</v>
+        <v>0.4231927753499053</v>
       </c>
       <c r="T78">
-        <v>3.497606715109185</v>
+        <v>3.649676572287845</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08438014118631366</v>
+        <v>0.08328429519688102</v>
       </c>
       <c r="W78">
-        <v>0.2159031627082673</v>
+        <v>0.2161615631925755</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3375205647452547</v>
+        <v>0.3331371807875241</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2637787419887613</v>
+        <v>0.2656787419887613</v>
       </c>
       <c r="C79">
-        <v>-15.64990393763541</v>
+        <v>-16.30265815112196</v>
       </c>
       <c r="D79">
-        <v>19.86479606236459</v>
+        <v>19.69314184887804</v>
       </c>
       <c r="E79">
-        <v>35.7347</v>
+        <v>36.2158</v>
       </c>
       <c r="F79">
-        <v>37.0447</v>
+        <v>37.5258</v>
       </c>
       <c r="G79">
         <v>1.53</v>
@@ -7765,37 +7765,37 @@
         <v>2.91</v>
       </c>
       <c r="M79">
-        <v>8.73514026</v>
+        <v>8.848583640000001</v>
       </c>
       <c r="N79">
-        <v>-5.82514026</v>
+        <v>-5.938583640000001</v>
       </c>
       <c r="O79">
-        <v>-1.456285065</v>
+        <v>-1.48464591</v>
       </c>
       <c r="P79">
-        <v>-4.368855195</v>
+        <v>-4.453937730000001</v>
       </c>
       <c r="Q79">
-        <v>-3.208855195</v>
+        <v>-3.293937730000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4231927753499053</v>
+        <v>0.4403469924112646</v>
       </c>
       <c r="T79">
-        <v>3.649676572287845</v>
+        <v>3.815570961937292</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08328429519688102</v>
+        <v>0.08221654782256202</v>
       </c>
       <c r="W79">
-        <v>0.2161615631925755</v>
+        <v>0.2164133380234399</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3331371807875241</v>
+        <v>0.3288661912902481</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2656787419887613</v>
+        <v>0.2675787419887613</v>
       </c>
       <c r="C80">
-        <v>-16.30265815112196</v>
+        <v>-16.95247120800621</v>
       </c>
       <c r="D80">
-        <v>19.69314184887804</v>
+        <v>19.52442879199379</v>
       </c>
       <c r="E80">
-        <v>36.2158</v>
+        <v>36.6969</v>
       </c>
       <c r="F80">
-        <v>37.5258</v>
+        <v>38.0069</v>
       </c>
       <c r="G80">
         <v>1.53</v>
@@ -7847,37 +7847,37 @@
         <v>2.91</v>
       </c>
       <c r="M80">
-        <v>8.848583640000001</v>
+        <v>8.962027020000001</v>
       </c>
       <c r="N80">
-        <v>-5.938583640000001</v>
+        <v>-6.052027020000001</v>
       </c>
       <c r="O80">
-        <v>-1.48464591</v>
+        <v>-1.513006755</v>
       </c>
       <c r="P80">
-        <v>-4.453937730000001</v>
+        <v>-4.539020265</v>
       </c>
       <c r="Q80">
-        <v>-3.293937730000001</v>
+        <v>-3.379020265</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4403469924112646</v>
+        <v>0.4591349444308487</v>
       </c>
       <c r="T80">
-        <v>3.815570961937292</v>
+        <v>3.997264817267641</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08221654782256202</v>
+        <v>0.08117583202733972</v>
       </c>
       <c r="W80">
-        <v>0.2164133380234399</v>
+        <v>0.2166587388079533</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3288661912902481</v>
+        <v>0.3247033281093589</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2675787419887613</v>
+        <v>0.2694787419887613</v>
       </c>
       <c r="C81">
-        <v>-16.95247120800621</v>
+        <v>-17.5994180577111</v>
       </c>
       <c r="D81">
-        <v>19.52442879199379</v>
+        <v>19.3585819422889</v>
       </c>
       <c r="E81">
-        <v>36.6969</v>
+        <v>37.178</v>
       </c>
       <c r="F81">
-        <v>38.0069</v>
+        <v>38.488</v>
       </c>
       <c r="G81">
         <v>1.53</v>
@@ -7929,37 +7929,37 @@
         <v>2.91</v>
       </c>
       <c r="M81">
-        <v>8.962027020000001</v>
+        <v>9.0754704</v>
       </c>
       <c r="N81">
-        <v>-6.052027020000001</v>
+        <v>-6.1654704</v>
       </c>
       <c r="O81">
-        <v>-1.513006755</v>
+        <v>-1.5413676</v>
       </c>
       <c r="P81">
-        <v>-4.539020265</v>
+        <v>-4.6241028</v>
       </c>
       <c r="Q81">
-        <v>-3.379020265</v>
+        <v>-3.4641028</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4591349444308487</v>
+        <v>0.4798016916523911</v>
       </c>
       <c r="T81">
-        <v>3.997264817267641</v>
+        <v>4.197128058131022</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08117583202733972</v>
+        <v>0.08016113412699798</v>
       </c>
       <c r="W81">
-        <v>0.2166587388079533</v>
+        <v>0.2168980045728539</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3247033281093589</v>
+        <v>0.320644536507992</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2694787419887613</v>
+        <v>0.2713787419887613</v>
       </c>
       <c r="C82">
-        <v>-17.5994180577111</v>
+        <v>-18.2435711245297</v>
       </c>
       <c r="D82">
-        <v>19.3585819422889</v>
+        <v>19.1955288754703</v>
       </c>
       <c r="E82">
-        <v>37.178</v>
+        <v>37.6591</v>
       </c>
       <c r="F82">
-        <v>38.488</v>
+        <v>38.9691</v>
       </c>
       <c r="G82">
         <v>1.53</v>
@@ -8011,37 +8011,37 @@
         <v>2.91</v>
       </c>
       <c r="M82">
-        <v>9.0754704</v>
+        <v>9.188913780000002</v>
       </c>
       <c r="N82">
-        <v>-6.1654704</v>
+        <v>-6.278913780000002</v>
       </c>
       <c r="O82">
-        <v>-1.5413676</v>
+        <v>-1.569728445</v>
       </c>
       <c r="P82">
-        <v>-4.6241028</v>
+        <v>-4.709185335000001</v>
       </c>
       <c r="Q82">
-        <v>-3.4641028</v>
+        <v>-3.549185335000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4798016916523911</v>
+        <v>0.5026438859498853</v>
       </c>
       <c r="T82">
-        <v>4.197128058131022</v>
+        <v>4.418029534874759</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08016113412699798</v>
+        <v>0.07917149049580047</v>
       </c>
       <c r="W82">
-        <v>0.2168980045728539</v>
+        <v>0.2171313625410903</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.320644536507992</v>
+        <v>0.3166859619832019</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2713787419887613</v>
+        <v>0.2732787419887613</v>
       </c>
       <c r="C83">
-        <v>-18.2435711245297</v>
+        <v>-18.88500041308008</v>
       </c>
       <c r="D83">
-        <v>19.1955288754703</v>
+        <v>19.03519958691992</v>
       </c>
       <c r="E83">
-        <v>37.6591</v>
+        <v>38.1402</v>
       </c>
       <c r="F83">
-        <v>38.9691</v>
+        <v>39.4502</v>
       </c>
       <c r="G83">
         <v>1.53</v>
@@ -8093,37 +8093,37 @@
         <v>2.91</v>
       </c>
       <c r="M83">
-        <v>9.188913780000002</v>
+        <v>9.302357160000001</v>
       </c>
       <c r="N83">
-        <v>-6.278913780000002</v>
+        <v>-6.392357160000001</v>
       </c>
       <c r="O83">
-        <v>-1.569728445</v>
+        <v>-1.59808929</v>
       </c>
       <c r="P83">
-        <v>-4.709185335000001</v>
+        <v>-4.794267870000001</v>
       </c>
       <c r="Q83">
-        <v>-3.549185335000001</v>
+        <v>-3.63426787</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5026438859498853</v>
+        <v>0.5280241018359901</v>
       </c>
       <c r="T83">
-        <v>4.418029534874759</v>
+        <v>4.66347562014558</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07917149049580047</v>
+        <v>0.07820598451414436</v>
       </c>
       <c r="W83">
-        <v>0.2171313625410903</v>
+        <v>0.2173590288515648</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3166859619832019</v>
+        <v>0.3128239380565775</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2732787419887613</v>
+        <v>0.2751787419887614</v>
       </c>
       <c r="C84">
-        <v>-18.88500041308008</v>
+        <v>-19.52377360851909</v>
       </c>
       <c r="D84">
-        <v>19.03519958691992</v>
+        <v>18.87752639148091</v>
       </c>
       <c r="E84">
-        <v>38.1402</v>
+        <v>38.6213</v>
       </c>
       <c r="F84">
-        <v>39.4502</v>
+        <v>39.9313</v>
       </c>
       <c r="G84">
         <v>1.53</v>
@@ -8175,37 +8175,37 @@
         <v>2.91</v>
       </c>
       <c r="M84">
-        <v>9.302357160000001</v>
+        <v>9.415800540000001</v>
       </c>
       <c r="N84">
-        <v>-6.392357160000001</v>
+        <v>-6.505800540000001</v>
       </c>
       <c r="O84">
-        <v>-1.59808929</v>
+        <v>-1.626450135</v>
       </c>
       <c r="P84">
-        <v>-4.794267870000001</v>
+        <v>-4.879350405</v>
       </c>
       <c r="Q84">
-        <v>-3.63426787</v>
+        <v>-3.719350405</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5280241018359901</v>
+        <v>0.5563902254734013</v>
       </c>
       <c r="T84">
-        <v>4.66347562014558</v>
+        <v>4.937797715448262</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07820598451414436</v>
+        <v>0.07726374373686552</v>
       </c>
       <c r="W84">
-        <v>0.2173590288515648</v>
+        <v>0.2175812092268471</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3128239380565775</v>
+        <v>0.309054974947462</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2751787419887614</v>
+        <v>0.2770787419887614</v>
       </c>
       <c r="C85">
-        <v>-19.52377360851909</v>
+        <v>-20.15995617181649</v>
       </c>
       <c r="D85">
-        <v>18.87752639148091</v>
+        <v>18.72244382818352</v>
       </c>
       <c r="E85">
-        <v>38.6213</v>
+        <v>39.1024</v>
       </c>
       <c r="F85">
-        <v>39.9313</v>
+        <v>40.41240000000001</v>
       </c>
       <c r="G85">
         <v>1.53</v>
@@ -8257,37 +8257,37 @@
         <v>2.91</v>
       </c>
       <c r="M85">
-        <v>9.415800540000001</v>
+        <v>9.529243920000001</v>
       </c>
       <c r="N85">
-        <v>-6.505800540000001</v>
+        <v>-6.619243920000001</v>
       </c>
       <c r="O85">
-        <v>-1.626450135</v>
+        <v>-1.65481098</v>
       </c>
       <c r="P85">
-        <v>-4.879350405</v>
+        <v>-4.96443294</v>
       </c>
       <c r="Q85">
-        <v>-3.719350405</v>
+        <v>-3.80443294</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5563902254734013</v>
+        <v>0.5883021145654891</v>
       </c>
       <c r="T85">
-        <v>4.937797715448262</v>
+        <v>5.24641007266378</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07726374373686552</v>
+        <v>0.0763439372638076</v>
       </c>
       <c r="W85">
-        <v>0.2175812092268471</v>
+        <v>0.2177980995931942</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.309054974947462</v>
+        <v>0.3053757490552303</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2770787419887613</v>
+        <v>0.2789787419887613</v>
       </c>
       <c r="C86">
-        <v>-20.15995617181648</v>
+        <v>-20.79361143037115</v>
       </c>
       <c r="D86">
-        <v>18.72244382818352</v>
+        <v>18.56988856962885</v>
       </c>
       <c r="E86">
-        <v>39.1024</v>
+        <v>39.58349999999999</v>
       </c>
       <c r="F86">
-        <v>40.4124</v>
+        <v>40.8935</v>
       </c>
       <c r="G86">
         <v>1.53</v>
@@ -8339,37 +8339,37 @@
         <v>2.91</v>
       </c>
       <c r="M86">
-        <v>9.529243920000001</v>
+        <v>9.642687299999999</v>
       </c>
       <c r="N86">
-        <v>-6.619243920000001</v>
+        <v>-6.732687299999998</v>
       </c>
       <c r="O86">
-        <v>-1.65481098</v>
+        <v>-1.683171825</v>
       </c>
       <c r="P86">
-        <v>-4.96443294</v>
+        <v>-5.049515474999999</v>
       </c>
       <c r="Q86">
-        <v>-3.80443294</v>
+        <v>-3.889515474999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5883021145654886</v>
+        <v>0.6244689222031879</v>
       </c>
       <c r="T86">
-        <v>5.246410072663775</v>
+        <v>5.596170744174694</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0763439372638076</v>
+        <v>0.07544577329599811</v>
       </c>
       <c r="W86">
-        <v>0.2177980995931942</v>
+        <v>0.2180098866568037</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3053757490552303</v>
+        <v>0.3017830931839924</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2789787419887613</v>
+        <v>0.2808787419887613</v>
       </c>
       <c r="C87">
-        <v>-20.79361143037115</v>
+        <v>-21.42480066423298</v>
       </c>
       <c r="D87">
-        <v>18.56988856962885</v>
+        <v>18.41979933576702</v>
       </c>
       <c r="E87">
-        <v>39.58349999999999</v>
+        <v>40.0646</v>
       </c>
       <c r="F87">
-        <v>40.8935</v>
+        <v>41.3746</v>
       </c>
       <c r="G87">
         <v>1.53</v>
@@ -8421,37 +8421,37 @@
         <v>2.91</v>
       </c>
       <c r="M87">
-        <v>9.642687299999999</v>
+        <v>9.75613068</v>
       </c>
       <c r="N87">
-        <v>-6.732687299999998</v>
+        <v>-6.84613068</v>
       </c>
       <c r="O87">
-        <v>-1.683171825</v>
+        <v>-1.71153267</v>
       </c>
       <c r="P87">
-        <v>-5.049515474999999</v>
+        <v>-5.134598009999999</v>
       </c>
       <c r="Q87">
-        <v>-3.889515474999999</v>
+        <v>-3.974598009999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6244689222031879</v>
+        <v>0.6658024166462728</v>
       </c>
       <c r="T87">
-        <v>5.596170744174694</v>
+        <v>5.995897225901459</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07544577329599811</v>
+        <v>0.07456849686232371</v>
       </c>
       <c r="W87">
-        <v>0.2180098866568037</v>
+        <v>0.2182167484398641</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3017830931839924</v>
+        <v>0.2982739874492948</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2808787419887613</v>
+        <v>0.2827787419887613</v>
       </c>
       <c r="C88">
-        <v>-21.42480066423298</v>
+        <v>-22.0535831881769</v>
       </c>
       <c r="D88">
-        <v>18.41979933576702</v>
+        <v>18.2721168118231</v>
       </c>
       <c r="E88">
-        <v>40.0646</v>
+        <v>40.5457</v>
       </c>
       <c r="F88">
-        <v>41.3746</v>
+        <v>41.8557</v>
       </c>
       <c r="G88">
         <v>1.53</v>
@@ -8503,37 +8503,37 @@
         <v>2.91</v>
       </c>
       <c r="M88">
-        <v>9.75613068</v>
+        <v>9.86957406</v>
       </c>
       <c r="N88">
-        <v>-6.84613068</v>
+        <v>-6.95957406</v>
       </c>
       <c r="O88">
-        <v>-1.71153267</v>
+        <v>-1.739893515</v>
       </c>
       <c r="P88">
-        <v>-5.134598009999999</v>
+        <v>-5.219680544999999</v>
       </c>
       <c r="Q88">
-        <v>-3.974598009999999</v>
+        <v>-4.059680544999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6658024166462728</v>
+        <v>0.7134949102344477</v>
       </c>
       <c r="T88">
-        <v>5.995897225901459</v>
+        <v>6.45712008943234</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07456849686232371</v>
+        <v>0.07371138770298666</v>
       </c>
       <c r="W88">
-        <v>0.2182167484398641</v>
+        <v>0.2184188547796357</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2982739874492948</v>
+        <v>0.2948455508119466</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2827787419887613</v>
+        <v>0.2846787419887613</v>
       </c>
       <c r="C89">
-        <v>-22.0535831881769</v>
+        <v>-22.68001642986023</v>
       </c>
       <c r="D89">
-        <v>18.2721168118231</v>
+        <v>18.12678357013976</v>
       </c>
       <c r="E89">
-        <v>40.5457</v>
+        <v>41.02679999999999</v>
       </c>
       <c r="F89">
-        <v>41.8557</v>
+        <v>42.3368</v>
       </c>
       <c r="G89">
         <v>1.53</v>
@@ -8585,37 +8585,37 @@
         <v>2.91</v>
       </c>
       <c r="M89">
-        <v>9.86957406</v>
+        <v>9.983017439999999</v>
       </c>
       <c r="N89">
-        <v>-6.95957406</v>
+        <v>-7.073017439999999</v>
       </c>
       <c r="O89">
-        <v>-1.739893515</v>
+        <v>-1.76825436</v>
       </c>
       <c r="P89">
-        <v>-5.219680544999999</v>
+        <v>-5.304763079999999</v>
       </c>
       <c r="Q89">
-        <v>-4.059680544999999</v>
+        <v>-4.144763079999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7134949102344477</v>
+        <v>0.7691361527539851</v>
       </c>
       <c r="T89">
-        <v>6.45712008943234</v>
+        <v>6.995213430218369</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07371138770298666</v>
+        <v>0.0728737582972709</v>
       </c>
       <c r="W89">
-        <v>0.2184188547796357</v>
+        <v>0.2186163677935035</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2948455508119466</v>
+        <v>0.2914950331890835</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2846787419887613</v>
+        <v>0.2865787419887613</v>
       </c>
       <c r="C90">
-        <v>-22.68001642986023</v>
+        <v>-23.30415600427945</v>
       </c>
       <c r="D90">
-        <v>18.12678357013976</v>
+        <v>17.98374399572055</v>
       </c>
       <c r="E90">
-        <v>41.02679999999999</v>
+        <v>41.5079</v>
       </c>
       <c r="F90">
-        <v>42.3368</v>
+        <v>42.8179</v>
       </c>
       <c r="G90">
         <v>1.53</v>
@@ -8667,37 +8667,37 @@
         <v>2.91</v>
       </c>
       <c r="M90">
-        <v>9.983017439999999</v>
+        <v>10.09646082</v>
       </c>
       <c r="N90">
-        <v>-7.073017439999999</v>
+        <v>-7.186460820000001</v>
       </c>
       <c r="O90">
-        <v>-1.76825436</v>
+        <v>-1.796615205</v>
       </c>
       <c r="P90">
-        <v>-5.304763079999999</v>
+        <v>-5.389845615</v>
       </c>
       <c r="Q90">
-        <v>-4.144763079999999</v>
+        <v>-4.229845615</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7691361527539851</v>
+        <v>0.8348939848225292</v>
       </c>
       <c r="T90">
-        <v>6.995213430218369</v>
+        <v>7.631141923874584</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0728737582972709</v>
+        <v>0.07205495202426784</v>
       </c>
       <c r="W90">
-        <v>0.2186163677935035</v>
+        <v>0.2188094423126777</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2914950331890835</v>
+        <v>0.2882198080970714</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2865787419887613</v>
+        <v>0.2884787419887613</v>
       </c>
       <c r="C91">
-        <v>-23.30415600427945</v>
+        <v>-23.92605578472932</v>
       </c>
       <c r="D91">
-        <v>17.98374399572055</v>
+        <v>17.84294421527067</v>
       </c>
       <c r="E91">
-        <v>41.5079</v>
+        <v>41.989</v>
       </c>
       <c r="F91">
-        <v>42.8179</v>
+        <v>43.299</v>
       </c>
       <c r="G91">
         <v>1.53</v>
@@ -8749,37 +8749,37 @@
         <v>2.91</v>
       </c>
       <c r="M91">
-        <v>10.09646082</v>
+        <v>10.2099042</v>
       </c>
       <c r="N91">
-        <v>-7.186460820000001</v>
+        <v>-7.2999042</v>
       </c>
       <c r="O91">
-        <v>-1.796615205</v>
+        <v>-1.82497605</v>
       </c>
       <c r="P91">
-        <v>-5.389845615</v>
+        <v>-5.47492815</v>
       </c>
       <c r="Q91">
-        <v>-4.229845615</v>
+        <v>-4.31492815</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8348939848225292</v>
+        <v>0.9138033833047822</v>
       </c>
       <c r="T91">
-        <v>7.631141923874584</v>
+        <v>8.394256116262044</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07205495202426784</v>
+        <v>0.07125434144622042</v>
       </c>
       <c r="W91">
-        <v>0.2188094423126777</v>
+        <v>0.2189982262869812</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2882198080970714</v>
+        <v>0.2850173657848817</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2884787419887613</v>
+        <v>0.2903787419887613</v>
       </c>
       <c r="C92">
-        <v>-23.92605578472932</v>
+        <v>-24.54576797045466</v>
       </c>
       <c r="D92">
-        <v>17.84294421527067</v>
+        <v>17.70433202954534</v>
       </c>
       <c r="E92">
-        <v>41.989</v>
+        <v>42.4701</v>
       </c>
       <c r="F92">
-        <v>43.299</v>
+        <v>43.7801</v>
       </c>
       <c r="G92">
         <v>1.53</v>
@@ -8831,37 +8831,37 @@
         <v>2.91</v>
       </c>
       <c r="M92">
-        <v>10.2099042</v>
+        <v>10.32334758</v>
       </c>
       <c r="N92">
-        <v>-7.2999042</v>
+        <v>-7.413347580000002</v>
       </c>
       <c r="O92">
-        <v>-1.82497605</v>
+        <v>-1.853336895</v>
       </c>
       <c r="P92">
-        <v>-5.47492815</v>
+        <v>-5.560010685000002</v>
       </c>
       <c r="Q92">
-        <v>-4.31492815</v>
+        <v>-4.400010685000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9138033833047822</v>
+        <v>1.01024820367198</v>
       </c>
       <c r="T92">
-        <v>8.394256116262044</v>
+        <v>9.326951240291161</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07125434144622042</v>
+        <v>0.07047132670505316</v>
       </c>
       <c r="W92">
-        <v>0.2189982262869812</v>
+        <v>0.2191828611629485</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2850173657848817</v>
+        <v>0.2818853068202126</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2903787419887613</v>
+        <v>0.2922787419887614</v>
       </c>
       <c r="C93">
-        <v>-24.54576797045466</v>
+        <v>-25.16334315117296</v>
       </c>
       <c r="D93">
-        <v>17.70433202954534</v>
+        <v>17.56785684882704</v>
       </c>
       <c r="E93">
-        <v>42.4701</v>
+        <v>42.9512</v>
       </c>
       <c r="F93">
-        <v>43.7801</v>
+        <v>44.2612</v>
       </c>
       <c r="G93">
         <v>1.53</v>
@@ -8913,37 +8913,37 @@
         <v>2.91</v>
       </c>
       <c r="M93">
-        <v>10.32334758</v>
+        <v>10.43679096</v>
       </c>
       <c r="N93">
-        <v>-7.413347580000002</v>
+        <v>-7.526790960000001</v>
       </c>
       <c r="O93">
-        <v>-1.853336895</v>
+        <v>-1.88169774</v>
       </c>
       <c r="P93">
-        <v>-5.560010685000002</v>
+        <v>-5.645093220000001</v>
       </c>
       <c r="Q93">
-        <v>-4.400010685000002</v>
+        <v>-4.485093220000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.01024820367198</v>
+        <v>1.130804229130978</v>
       </c>
       <c r="T93">
-        <v>9.326951240291161</v>
+        <v>10.49282014532756</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07047132670505316</v>
+        <v>0.06970533402347649</v>
       </c>
       <c r="W93">
-        <v>0.2191828611629485</v>
+        <v>0.2193634822372643</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2818853068202126</v>
+        <v>0.278821336093906</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2922787419887614</v>
+        <v>0.2941787419887613</v>
       </c>
       <c r="C94">
-        <v>-25.16334315117296</v>
+        <v>-25.77883036863573</v>
       </c>
       <c r="D94">
-        <v>17.56785684882704</v>
+        <v>17.43346963136427</v>
       </c>
       <c r="E94">
-        <v>42.9512</v>
+        <v>43.4323</v>
       </c>
       <c r="F94">
-        <v>44.2612</v>
+        <v>44.7423</v>
       </c>
       <c r="G94">
         <v>1.53</v>
@@ -8995,37 +8995,37 @@
         <v>2.91</v>
       </c>
       <c r="M94">
-        <v>10.43679096</v>
+        <v>10.55023434</v>
       </c>
       <c r="N94">
-        <v>-7.526790960000001</v>
+        <v>-7.640234340000001</v>
       </c>
       <c r="O94">
-        <v>-1.88169774</v>
+        <v>-1.910058585</v>
       </c>
       <c r="P94">
-        <v>-5.645093220000001</v>
+        <v>-5.730175755000001</v>
       </c>
       <c r="Q94">
-        <v>-4.485093220000001</v>
+        <v>-4.570175755000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.130804229130978</v>
+        <v>1.285804833292547</v>
       </c>
       <c r="T94">
-        <v>10.49282014532756</v>
+        <v>11.99179445180293</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06970533402347649</v>
+        <v>0.06895581430279396</v>
       </c>
       <c r="W94">
-        <v>0.2193634822372643</v>
+        <v>0.2195402189874012</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.278821336093906</v>
+        <v>0.2758232572111758</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2941787419887613</v>
+        <v>0.2960787419887613</v>
       </c>
       <c r="C95">
-        <v>-25.77883036863573</v>
+        <v>-26.39227717538562</v>
       </c>
       <c r="D95">
-        <v>17.43346963136427</v>
+        <v>17.30112282461439</v>
       </c>
       <c r="E95">
-        <v>43.4323</v>
+        <v>43.9134</v>
       </c>
       <c r="F95">
-        <v>44.7423</v>
+        <v>45.22340000000001</v>
       </c>
       <c r="G95">
         <v>1.53</v>
@@ -9077,37 +9077,37 @@
         <v>2.91</v>
       </c>
       <c r="M95">
-        <v>10.55023434</v>
+        <v>10.66367772</v>
       </c>
       <c r="N95">
-        <v>-7.640234340000001</v>
+        <v>-7.753677720000001</v>
       </c>
       <c r="O95">
-        <v>-1.910058585</v>
+        <v>-1.93841943</v>
       </c>
       <c r="P95">
-        <v>-5.730175755000001</v>
+        <v>-5.815258290000001</v>
       </c>
       <c r="Q95">
-        <v>-4.570175755000001</v>
+        <v>-4.655258290000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.285804833292547</v>
+        <v>1.492472305507971</v>
       </c>
       <c r="T95">
-        <v>11.99179445180293</v>
+        <v>13.99042686043675</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06895581430279396</v>
+        <v>0.06822224181021104</v>
       </c>
       <c r="W95">
-        <v>0.2195402189874012</v>
+        <v>0.2197131953811522</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2758232572111758</v>
+        <v>0.2728889672408442</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2960787419887613</v>
+        <v>0.2979787419887613</v>
       </c>
       <c r="C96">
-        <v>-26.39227717538562</v>
+        <v>-27.00372969085749</v>
       </c>
       <c r="D96">
-        <v>17.30112282461439</v>
+        <v>17.17077030914251</v>
       </c>
       <c r="E96">
-        <v>43.9134</v>
+        <v>44.3945</v>
       </c>
       <c r="F96">
-        <v>45.22340000000001</v>
+        <v>45.7045</v>
       </c>
       <c r="G96">
         <v>1.53</v>
@@ -9159,37 +9159,37 @@
         <v>2.91</v>
       </c>
       <c r="M96">
-        <v>10.66367772</v>
+        <v>10.7771211</v>
       </c>
       <c r="N96">
-        <v>-7.753677720000001</v>
+        <v>-7.8671211</v>
       </c>
       <c r="O96">
-        <v>-1.93841943</v>
+        <v>-1.966780275</v>
       </c>
       <c r="P96">
-        <v>-5.815258290000001</v>
+        <v>-5.900340825000001</v>
       </c>
       <c r="Q96">
-        <v>-4.655258290000001</v>
+        <v>-4.740340825000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.492472305507971</v>
+        <v>1.781806766609567</v>
       </c>
       <c r="T96">
-        <v>13.99042686043675</v>
+        <v>16.78851223252411</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06822224181021104</v>
+        <v>0.06750411294905093</v>
       </c>
       <c r="W96">
-        <v>0.2197131953811522</v>
+        <v>0.2198825301666138</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2728889672408442</v>
+        <v>0.2700164517962037</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2979787419887613</v>
+        <v>0.2998787419887613</v>
       </c>
       <c r="C97">
-        <v>-27.00372969085749</v>
+        <v>-27.61323265496227</v>
       </c>
       <c r="D97">
-        <v>17.17077030914251</v>
+        <v>17.04236734503773</v>
       </c>
       <c r="E97">
-        <v>44.3945</v>
+        <v>44.8756</v>
       </c>
       <c r="F97">
-        <v>45.7045</v>
+        <v>46.1856</v>
       </c>
       <c r="G97">
         <v>1.53</v>
@@ -9241,37 +9241,37 @@
         <v>2.91</v>
       </c>
       <c r="M97">
-        <v>10.7771211</v>
+        <v>10.89056448</v>
       </c>
       <c r="N97">
-        <v>-7.8671211</v>
+        <v>-7.98056448</v>
       </c>
       <c r="O97">
-        <v>-1.966780275</v>
+        <v>-1.99514112</v>
       </c>
       <c r="P97">
-        <v>-5.900340825000001</v>
+        <v>-5.98542336</v>
       </c>
       <c r="Q97">
-        <v>-4.740340825000001</v>
+        <v>-4.82542336</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.781806766609567</v>
+        <v>2.215808458261959</v>
       </c>
       <c r="T97">
-        <v>16.78851223252411</v>
+        <v>20.98564029065514</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06750411294905093</v>
+        <v>0.06680094510583165</v>
       </c>
       <c r="W97">
-        <v>0.2198825301666138</v>
+        <v>0.2200483371440449</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2700164517962037</v>
+        <v>0.2672037804233266</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2998787419887613</v>
+        <v>0.3017787419887613</v>
       </c>
       <c r="C98">
-        <v>-27.61323265496227</v>
+        <v>-28.22082947928447</v>
       </c>
       <c r="D98">
-        <v>17.04236734503773</v>
+        <v>16.91587052071553</v>
       </c>
       <c r="E98">
-        <v>44.8756</v>
+        <v>45.3567</v>
       </c>
       <c r="F98">
-        <v>46.1856</v>
+        <v>46.6667</v>
       </c>
       <c r="G98">
         <v>1.53</v>
@@ -9323,37 +9323,37 @@
         <v>2.91</v>
       </c>
       <c r="M98">
-        <v>10.89056448</v>
+        <v>11.00400786</v>
       </c>
       <c r="N98">
-        <v>-7.98056448</v>
+        <v>-8.09400786</v>
       </c>
       <c r="O98">
-        <v>-1.99514112</v>
+        <v>-2.023501965</v>
       </c>
       <c r="P98">
-        <v>-5.98542336</v>
+        <v>-6.070505895</v>
       </c>
       <c r="Q98">
-        <v>-4.82542336</v>
+        <v>-4.910505895</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.215808458261954</v>
+        <v>2.939144611015938</v>
       </c>
       <c r="T98">
-        <v>20.98564029065509</v>
+        <v>27.98085372087345</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06680094510583165</v>
+        <v>0.06611227556865813</v>
       </c>
       <c r="W98">
-        <v>0.2200483371440449</v>
+        <v>0.2202107254209104</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2672037804233266</v>
+        <v>0.2644491022746325</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3017787419887613</v>
+        <v>0.3036787419887613</v>
       </c>
       <c r="C99">
-        <v>-28.22082947928447</v>
+        <v>-28.82656229601645</v>
       </c>
       <c r="D99">
-        <v>16.91587052071553</v>
+        <v>16.79123770398354</v>
       </c>
       <c r="E99">
-        <v>45.3567</v>
+        <v>45.83779999999999</v>
       </c>
       <c r="F99">
-        <v>46.6667</v>
+        <v>47.1478</v>
       </c>
       <c r="G99">
         <v>1.53</v>
@@ -9405,37 +9405,37 @@
         <v>2.91</v>
       </c>
       <c r="M99">
-        <v>11.00400786</v>
+        <v>11.11745124</v>
       </c>
       <c r="N99">
-        <v>-8.09400786</v>
+        <v>-8.207451239999999</v>
       </c>
       <c r="O99">
-        <v>-2.023501965</v>
+        <v>-2.05186281</v>
       </c>
       <c r="P99">
-        <v>-6.070505895</v>
+        <v>-6.15558843</v>
       </c>
       <c r="Q99">
-        <v>-4.910505895</v>
+        <v>-4.99558843</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.939144611015938</v>
+        <v>4.385816916523908</v>
       </c>
       <c r="T99">
-        <v>27.98085372087345</v>
+        <v>41.97128058131018</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06611227556865813</v>
+        <v>0.0654376605118351</v>
       </c>
       <c r="W99">
-        <v>0.2202107254209104</v>
+        <v>0.2203697996513093</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2644491022746325</v>
+        <v>0.2617506420473403</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3036787419887613</v>
+        <v>0.3055787419887613</v>
       </c>
       <c r="C100">
-        <v>-28.82656229601645</v>
+        <v>-29.43047200474524</v>
       </c>
       <c r="D100">
-        <v>16.79123770398354</v>
+        <v>16.66842799525476</v>
       </c>
       <c r="E100">
-        <v>45.83779999999999</v>
+        <v>46.3189</v>
       </c>
       <c r="F100">
-        <v>47.1478</v>
+        <v>47.6289</v>
       </c>
       <c r="G100">
         <v>1.53</v>
@@ -9487,37 +9487,37 @@
         <v>2.91</v>
       </c>
       <c r="M100">
-        <v>11.11745124</v>
+        <v>11.23089462</v>
       </c>
       <c r="N100">
-        <v>-8.207451239999999</v>
+        <v>-8.320894620000001</v>
       </c>
       <c r="O100">
-        <v>-2.05186281</v>
+        <v>-2.080223655</v>
       </c>
       <c r="P100">
-        <v>-6.15558843</v>
+        <v>-6.240670965000001</v>
       </c>
       <c r="Q100">
-        <v>-4.99558843</v>
+        <v>-5.080670965</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.385816916523908</v>
+        <v>8.725833833047815</v>
       </c>
       <c r="T100">
-        <v>41.97128058131018</v>
+        <v>83.94256116262036</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0654376605118351</v>
+        <v>0.06477667404201856</v>
       </c>
       <c r="W100">
-        <v>0.2203697996513093</v>
+        <v>0.220525660260892</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2617506420473403</v>
+        <v>0.2591066961680742</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3055787419887613</v>
-      </c>
-      <c r="C101">
-        <v>-29.43047200474524</v>
-      </c>
-      <c r="D101">
-        <v>16.66842799525476</v>
-      </c>
-      <c r="E101">
-        <v>46.3189</v>
-      </c>
-      <c r="F101">
-        <v>47.6289</v>
-      </c>
-      <c r="G101">
-        <v>1.53</v>
-      </c>
-      <c r="H101">
-        <v>46.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.07</v>
-      </c>
-      <c r="K101">
-        <v>1.16</v>
-      </c>
-      <c r="L101">
-        <v>2.91</v>
-      </c>
-      <c r="M101">
-        <v>11.23089462</v>
-      </c>
-      <c r="N101">
-        <v>-8.320894620000001</v>
-      </c>
-      <c r="O101">
-        <v>-2.080223655</v>
-      </c>
-      <c r="P101">
-        <v>-6.240670965000001</v>
-      </c>
-      <c r="Q101">
-        <v>-5.080670965</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.725833833047815</v>
-      </c>
-      <c r="T101">
-        <v>83.94256116262036</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06477667404201856</v>
-      </c>
-      <c r="W101">
-        <v>0.220525660260892</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2591066961680742</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
